--- a/sequencer input v3.xlsx
+++ b/sequencer input v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ui208936\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C555BE4B-150C-458F-B465-5041B0A7EFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2518A340-5E20-483E-B911-89DE8A751521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-2832" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{45D2DF17-6F7C-45FD-9E14-08090A3A3102}"/>
+    <workbookView xWindow="-67320" yWindow="-3525" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{45D2DF17-6F7C-45FD-9E14-08090A3A3102}"/>
   </bookViews>
   <sheets>
     <sheet name="FOU data" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="158">
   <si>
     <t>Structure</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>WTG ID</t>
-  </si>
-  <si>
-    <t>FOU</t>
   </si>
   <si>
     <t xml:space="preserve">Easy </t>
@@ -533,13 +530,22 @@
     <t xml:space="preserve">IAC burial  </t>
   </si>
   <si>
-    <t>Scour armour</t>
-  </si>
-  <si>
-    <t>Scour filter</t>
-  </si>
-  <si>
-    <t>WTG commisoning</t>
+    <t>SST installation</t>
+  </si>
+  <si>
+    <t>Filter Layer</t>
+  </si>
+  <si>
+    <t>Armour Layer</t>
+  </si>
+  <si>
+    <t>WTG installation</t>
+  </si>
+  <si>
+    <t>WTG commisioning</t>
+  </si>
+  <si>
+    <t>FOU installation</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1407,7 @@
         <v>58</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -1416,10 +1422,10 @@
         <v>57</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>55</v>
@@ -1428,16 +1434,16 @@
         <v>54</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="N1" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -1462,10 +1468,10 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1494,10 +1500,10 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -1526,10 +1532,10 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -1558,10 +1564,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -1590,10 +1596,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1622,10 +1628,10 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1654,10 +1660,10 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -1686,10 +1692,10 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -1718,10 +1724,10 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -1750,10 +1756,10 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -1782,10 +1788,10 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1814,10 +1820,10 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1846,10 +1852,10 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1878,10 +1884,10 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1910,10 +1916,10 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1942,10 +1948,10 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1974,10 +1980,10 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -2006,10 +2012,10 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -2038,10 +2044,10 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -2070,10 +2076,10 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -2102,10 +2108,10 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2134,10 +2140,10 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -2166,10 +2172,10 @@
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -2198,10 +2204,10 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -2230,10 +2236,10 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -2265,7 +2271,7 @@
         <v>56</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -2294,10 +2300,10 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -2329,7 +2335,7 @@
         <v>56</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -2358,10 +2364,10 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -2390,10 +2396,10 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -2422,10 +2428,10 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -2457,7 +2463,7 @@
         <v>56</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -2489,7 +2495,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -2521,7 +2527,7 @@
         <v>56</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -2553,7 +2559,7 @@
         <v>56</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -2582,10 +2588,10 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -2614,10 +2620,10 @@
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -2646,10 +2652,10 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -2678,10 +2684,10 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -2710,10 +2716,10 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -2745,7 +2751,7 @@
         <v>56</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2774,10 +2780,10 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2806,10 +2812,10 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2838,10 +2844,10 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2873,7 +2879,7 @@
         <v>56</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2966,7 +2972,7 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>56</v>
@@ -2998,7 +3004,7 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>56</v>
@@ -3030,7 +3036,7 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>56</v>
@@ -3042,13 +3048,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D52" s="15">
         <v>451560.92599999998</v>
@@ -3098,33 +3104,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="39" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="38" t="s">
+      <c r="E1" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="38" t="s">
-        <v>68</v>
-      </c>
       <c r="F1" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="38" t="s">
-        <v>63</v>
-      </c>
       <c r="H1" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="32" t="str">
         <f>F2&amp;"-"&amp;G2</f>
@@ -3134,13 +3140,13 @@
         <v>56</v>
       </c>
       <c r="D2" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="33" t="s">
-        <v>71</v>
-      </c>
       <c r="F2" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>51</v>
@@ -3151,7 +3157,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" ref="B3:B56" si="0">F3&amp;"-"&amp;G3</f>
@@ -3161,10 +3167,10 @@
         <v>56</v>
       </c>
       <c r="D3" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>70</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>71</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>51</v>
@@ -3173,12 +3179,12 @@
         <v>49</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3188,10 +3194,10 @@
         <v>56</v>
       </c>
       <c r="D4" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="29" t="s">
         <v>70</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>71</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>49</v>
@@ -3200,12 +3206,12 @@
         <v>48</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3215,10 +3221,10 @@
         <v>56</v>
       </c>
       <c r="D5" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="29" t="s">
         <v>70</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>71</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>48</v>
@@ -3227,12 +3233,12 @@
         <v>47</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3242,10 +3248,10 @@
         <v>56</v>
       </c>
       <c r="D6" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>70</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>71</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>47</v>
@@ -3254,12 +3260,12 @@
         <v>46</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3270,7 +3276,7 @@
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>46</v>
@@ -3279,12 +3285,12 @@
         <v>40</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3294,10 +3300,10 @@
         <v>56</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>40</v>
@@ -3306,12 +3312,12 @@
         <v>44</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3321,10 +3327,10 @@
         <v>56</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>44</v>
@@ -3333,12 +3339,12 @@
         <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3348,10 +3354,10 @@
         <v>56</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>30</v>
@@ -3360,12 +3366,12 @@
         <v>43</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3375,10 +3381,10 @@
         <v>56</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>43</v>
@@ -3387,12 +3393,12 @@
         <v>50</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="30" t="str">
         <f t="shared" si="0"/>
@@ -3402,16 +3408,16 @@
         <v>56</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>56</v>
@@ -3419,7 +3425,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="32" t="str">
         <f t="shared" si="0"/>
@@ -3429,13 +3435,13 @@
         <v>56</v>
       </c>
       <c r="D13" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>85</v>
-      </c>
       <c r="F13" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>45</v>
@@ -3446,7 +3452,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3456,10 +3462,10 @@
         <v>56</v>
       </c>
       <c r="D14" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>85</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>45</v>
@@ -3468,12 +3474,12 @@
         <v>36</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3483,10 +3489,10 @@
         <v>56</v>
       </c>
       <c r="D15" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>85</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>36</v>
@@ -3495,12 +3501,12 @@
         <v>37</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3510,10 +3516,10 @@
         <v>56</v>
       </c>
       <c r="D16" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>85</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>37</v>
@@ -3522,12 +3528,12 @@
         <v>6</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3537,10 +3543,10 @@
         <v>56</v>
       </c>
       <c r="D17" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>85</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>6</v>
@@ -3549,12 +3555,12 @@
         <v>38</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3565,7 +3571,7 @@
       </c>
       <c r="D18" s="28"/>
       <c r="E18" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>38</v>
@@ -3574,12 +3580,12 @@
         <v>22</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3589,10 +3595,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>22</v>
@@ -3601,12 +3607,12 @@
         <v>18</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3616,10 +3622,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>18</v>
@@ -3628,12 +3634,12 @@
         <v>27</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3643,10 +3649,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
@@ -3655,12 +3661,12 @@
         <v>31</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3670,10 +3676,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>31</v>
@@ -3682,12 +3688,12 @@
         <v>39</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="34" t="str">
         <f t="shared" si="0"/>
@@ -3697,16 +3703,16 @@
         <v>56</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>39</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>56</v>
@@ -3714,7 +3720,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="0"/>
@@ -3724,13 +3730,13 @@
         <v>56</v>
       </c>
       <c r="D24" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>98</v>
-      </c>
       <c r="F24" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>53</v>
@@ -3741,7 +3747,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B25" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3751,10 +3757,10 @@
         <v>56</v>
       </c>
       <c r="D25" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>53</v>
@@ -3763,12 +3769,12 @@
         <v>26</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B26" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3778,10 +3784,10 @@
         <v>56</v>
       </c>
       <c r="D26" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>26</v>
@@ -3790,12 +3796,12 @@
         <v>34</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B27" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3805,10 +3811,10 @@
         <v>56</v>
       </c>
       <c r="D27" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>34</v>
@@ -3817,12 +3823,12 @@
         <v>11</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B28" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3832,10 +3838,10 @@
         <v>56</v>
       </c>
       <c r="D28" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>11</v>
@@ -3844,12 +3850,12 @@
         <v>14</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B29" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3860,7 +3866,7 @@
       </c>
       <c r="D29" s="28"/>
       <c r="E29" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>14</v>
@@ -3869,12 +3875,12 @@
         <v>8</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B30" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3884,10 +3890,10 @@
         <v>56</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>8</v>
@@ -3896,12 +3902,12 @@
         <v>5</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3911,10 +3917,10 @@
         <v>56</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>5</v>
@@ -3923,12 +3929,12 @@
         <v>12</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3938,10 +3944,10 @@
         <v>56</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>12</v>
@@ -3950,12 +3956,12 @@
         <v>15</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B33" s="28" t="str">
         <f t="shared" si="0"/>
@@ -3965,10 +3971,10 @@
         <v>56</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>15</v>
@@ -3977,12 +3983,12 @@
         <v>42</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B34" s="30" t="str">
         <f t="shared" si="0"/>
@@ -3992,16 +3998,16 @@
         <v>56</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>42</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>56</v>
@@ -4009,7 +4015,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B35" s="32" t="str">
         <f t="shared" si="0"/>
@@ -4019,13 +4025,13 @@
         <v>56</v>
       </c>
       <c r="D35" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="E35" s="33" t="s">
-        <v>103</v>
-      </c>
       <c r="F35" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" s="19" t="s">
         <v>7</v>
@@ -4036,7 +4042,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4046,10 +4052,10 @@
         <v>56</v>
       </c>
       <c r="D36" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="29" t="s">
         <v>102</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>103</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>7</v>
@@ -4058,12 +4064,12 @@
         <v>21</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B37" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4073,10 +4079,10 @@
         <v>56</v>
       </c>
       <c r="D37" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="29" t="s">
         <v>102</v>
-      </c>
-      <c r="E37" s="29" t="s">
-        <v>103</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>21</v>
@@ -4085,12 +4091,12 @@
         <v>16</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B38" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4100,10 +4106,10 @@
         <v>56</v>
       </c>
       <c r="D38" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E38" s="29" t="s">
         <v>102</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>103</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>16</v>
@@ -4112,12 +4118,12 @@
         <v>4</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4127,10 +4133,10 @@
         <v>56</v>
       </c>
       <c r="D39" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="29" t="s">
         <v>102</v>
-      </c>
-      <c r="E39" s="29" t="s">
-        <v>103</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>4</v>
@@ -4139,12 +4145,12 @@
         <v>10</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B40" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4155,7 +4161,7 @@
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>10</v>
@@ -4164,12 +4170,12 @@
         <v>17</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B41" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4179,10 +4185,10 @@
         <v>56</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>17</v>
@@ -4191,12 +4197,12 @@
         <v>20</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B42" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4206,10 +4212,10 @@
         <v>56</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>20</v>
@@ -4218,12 +4224,12 @@
         <v>9</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B43" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4233,10 +4239,10 @@
         <v>56</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>9</v>
@@ -4245,12 +4251,12 @@
         <v>13</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B44" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4260,10 +4266,10 @@
         <v>56</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>13</v>
@@ -4272,12 +4278,12 @@
         <v>41</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45" s="34" t="str">
         <f t="shared" si="0"/>
@@ -4287,16 +4293,16 @@
         <v>56</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F45" s="14" t="s">
         <v>41</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>56</v>
@@ -4304,7 +4310,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
@@ -4314,13 +4320,13 @@
         <v>56</v>
       </c>
       <c r="D46" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="E46" s="27" t="s">
-        <v>117</v>
-      </c>
       <c r="F46" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>23</v>
@@ -4331,7 +4337,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B47" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4341,10 +4347,10 @@
         <v>56</v>
       </c>
       <c r="D47" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="29" t="s">
         <v>116</v>
-      </c>
-      <c r="E47" s="29" t="s">
-        <v>117</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>23</v>
@@ -4353,12 +4359,12 @@
         <v>19</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B48" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4368,10 +4374,10 @@
         <v>56</v>
       </c>
       <c r="D48" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E48" s="29" t="s">
         <v>116</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>117</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>19</v>
@@ -4380,12 +4386,12 @@
         <v>35</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B49" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4395,10 +4401,10 @@
         <v>56</v>
       </c>
       <c r="D49" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E49" s="29" t="s">
         <v>116</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>117</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>35</v>
@@ -4407,12 +4413,12 @@
         <v>29</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B50" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4422,10 +4428,10 @@
         <v>56</v>
       </c>
       <c r="D50" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" s="29" t="s">
         <v>116</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>117</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>29</v>
@@ -4434,12 +4440,12 @@
         <v>24</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B51" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4450,7 +4456,7 @@
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>24</v>
@@ -4459,12 +4465,12 @@
         <v>28</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B52" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4474,10 +4480,10 @@
         <v>56</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>28</v>
@@ -4486,12 +4492,12 @@
         <v>32</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B53" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4501,10 +4507,10 @@
         <v>56</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>32</v>
@@ -4513,12 +4519,12 @@
         <v>25</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B54" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4528,10 +4534,10 @@
         <v>56</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>25</v>
@@ -4540,12 +4546,12 @@
         <v>33</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B55" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4555,10 +4561,10 @@
         <v>56</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>33</v>
@@ -4567,12 +4573,12 @@
         <v>52</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B56" s="30" t="str">
         <f t="shared" si="0"/>
@@ -4582,16 +4588,16 @@
         <v>56</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F56" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>56</v>
@@ -4623,7 +4629,7 @@
         <v>58</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -4635,7 +4641,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -4655,7 +4661,7 @@
         <v>5926740.4285000004</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -4675,7 +4681,7 @@
         <v>5926754.4106999999</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4695,7 +4701,7 @@
         <v>5926765.4616999999</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -4715,7 +4721,7 @@
         <v>5926776.5153000001</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4735,7 +4741,7 @@
         <v>5926787.9123999998</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -4755,7 +4761,7 @@
         <v>5926798.8937999997</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -4775,7 +4781,7 @@
         <v>5926816.5809000004</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -4795,7 +4801,7 @@
         <v>5926821.4907999998</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -4815,7 +4821,7 @@
         <v>5926832.1205000002</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -4835,7 +4841,7 @@
         <v>5926841.9177000001</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -4855,7 +4861,7 @@
         <v>5926851.7503000004</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -4875,7 +4881,7 @@
         <v>5925672.8383999998</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -4895,7 +4901,7 @@
         <v>5925722.3081999999</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -4915,7 +4921,7 @@
         <v>5925744.102</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -4935,7 +4941,7 @@
         <v>5925598.8696999997</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -4955,7 +4961,7 @@
         <v>5925760.5027999999</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -4975,7 +4981,7 @@
         <v>5925750.5869000005</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -4995,7 +5001,7 @@
         <v>5925707.2302000001</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -5015,7 +5021,7 @@
         <v>5925473.7775999997</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -5035,7 +5041,7 @@
         <v>5925538.8964</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -5055,7 +5061,7 @@
         <v>5925738.2577999998</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -5075,7 +5081,7 @@
         <v>5924550.3740999997</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -5095,7 +5101,7 @@
         <v>5924530.9869999997</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -5115,7 +5121,7 @@
         <v>5924621.1495000003</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -5135,7 +5141,7 @@
         <v>5924472.1304000001</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -5155,7 +5161,7 @@
         <v>5924652.8443</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -5175,7 +5181,7 @@
         <v>5924460.3476999998</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -5195,7 +5201,7 @@
         <v>5924363.7493000003</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -5215,7 +5221,7 @@
         <v>5923335.0530000003</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -5235,7 +5241,7 @@
         <v>5922980.8535000002</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -5255,7 +5261,7 @@
         <v>5923540.4664000003</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -5275,7 +5281,7 @@
         <v>5923286.1697000004</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -5295,7 +5301,7 @@
         <v>5923568.3879000004</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -5315,7 +5321,7 @@
         <v>5923406.2419999996</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -5335,7 +5341,7 @@
         <v>5923167.5865000002</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -5355,7 +5361,7 @@
         <v>5923221.8696999997</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -5375,7 +5381,7 @@
         <v>5922267.1327</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -5395,7 +5401,7 @@
         <v>5921798.2410000004</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -5415,7 +5421,7 @@
         <v>5922377.7856000001</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -5435,7 +5441,7 @@
         <v>5922155.3957000002</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -5455,7 +5461,7 @@
         <v>5922329.3293000003</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -5475,7 +5481,7 @@
         <v>5921269.5873999996</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -5495,7 +5501,7 @@
         <v>5920800.6169999996</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -5515,7 +5521,7 @@
         <v>5921383.6398</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -5535,7 +5541,7 @@
         <v>5921209.0383000001</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -5555,7 +5561,7 @@
         <v>5921441.3432999998</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -5575,7 +5581,7 @@
         <v>5921513.1471999995</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -5595,7 +5601,7 @@
         <v>5920292.7520000003</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -5615,7 +5621,7 @@
         <v>5919830.1629999997</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -5635,18 +5641,18 @@
         <v>5920298.3925000001</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D52" s="15">
         <v>451560.92599999998</v>
@@ -5673,97 +5679,107 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C3D562A-0193-463C-8D4E-3D45B26E877E}">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="7" width="12.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="11.453125" customWidth="1"/>
-    <col min="12" max="12" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="12.6328125" customWidth="1"/>
+    <col min="10" max="10" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.453125" customWidth="1"/>
+    <col min="14" max="14" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="23"/>
       <c r="B1" s="39" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="C1" s="39"/>
       <c r="D1" s="40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E1" s="41"/>
       <c r="F1" s="40" t="s">
         <v>153</v>
       </c>
       <c r="G1" s="41"/>
-      <c r="H1" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="I1" s="39"/>
+      <c r="H1" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="I1" s="41"/>
       <c r="J1" s="39" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K1" s="39"/>
       <c r="L1" s="39" t="s">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="M1" s="39"/>
       <c r="N1" s="39" t="s">
         <v>155</v>
       </c>
       <c r="O1" s="39"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P1" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="D2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="F2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="H2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="J2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="L2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="N2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="24">
         <v>1</v>
       </c>
@@ -5775,53 +5791,61 @@
         <v>47575</v>
       </c>
       <c r="D3" s="25">
+        <f>B3+25</f>
+        <v>47599</v>
+      </c>
+      <c r="E3" s="25">
+        <f>D3+1</f>
+        <v>47600</v>
+      </c>
+      <c r="F3" s="25">
         <f>B3-30</f>
         <v>47544</v>
       </c>
-      <c r="E3" s="25">
-        <f>D3</f>
+      <c r="G3" s="25">
+        <f>F3</f>
         <v>47544</v>
       </c>
-      <c r="F3" s="25">
+      <c r="H3" s="25">
         <f>B3+30</f>
         <v>47604</v>
       </c>
-      <c r="G3" s="25">
-        <f>F3</f>
+      <c r="I3" s="25">
+        <f>H3</f>
         <v>47604</v>
       </c>
-      <c r="H3" s="25">
+      <c r="J3" s="25">
         <v>47696</v>
       </c>
-      <c r="I3" s="25">
-        <f t="shared" ref="I3:I34" si="1">H3+0.7</f>
+      <c r="K3" s="25">
+        <f t="shared" ref="K3:K34" si="1">J3+0.7</f>
         <v>47696.7</v>
       </c>
-      <c r="J3" s="25">
-        <f>H3+15</f>
+      <c r="L3" s="25">
+        <f>J3+15</f>
         <v>47711</v>
       </c>
-      <c r="K3" s="25">
-        <f>J3+1</f>
+      <c r="M3" s="25">
+        <f>L3+1</f>
         <v>47712</v>
       </c>
-      <c r="L3" s="9">
+      <c r="N3" s="9">
         <v>47908</v>
       </c>
-      <c r="M3" s="9">
-        <f>L4</f>
+      <c r="O3" s="9">
+        <f>N4</f>
         <v>47912</v>
       </c>
-      <c r="N3" s="42">
-        <f>L3+7</f>
+      <c r="P3" s="42">
+        <f>N3+7</f>
         <v>47915</v>
       </c>
-      <c r="O3" s="42">
-        <f>N3+5</f>
+      <c r="Q3" s="42">
+        <f>P3+5</f>
         <v>47920</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -5834,55 +5858,63 @@
         <v>47576</v>
       </c>
       <c r="D4" s="25">
-        <f t="shared" ref="D4:D57" si="3">B4-30</f>
+        <f t="shared" ref="D4:D57" si="3">B4+25</f>
+        <v>47600</v>
+      </c>
+      <c r="E4" s="25">
+        <f t="shared" ref="E4:E57" si="4">D4+1</f>
+        <v>47601</v>
+      </c>
+      <c r="F4" s="25">
+        <f>B4-30</f>
         <v>47545</v>
       </c>
-      <c r="E4" s="25">
-        <f t="shared" ref="E4:E57" si="4">D4</f>
+      <c r="G4" s="25">
+        <f t="shared" ref="G4:G52" si="5">F4</f>
         <v>47545</v>
       </c>
-      <c r="F4" s="25">
-        <f t="shared" ref="F4:F57" si="5">B4+30</f>
+      <c r="H4" s="25">
+        <f>B4+30</f>
         <v>47605</v>
       </c>
-      <c r="G4" s="25">
-        <f t="shared" ref="G4:G57" si="6">F4</f>
+      <c r="I4" s="25">
+        <f t="shared" ref="I4:I52" si="6">H4</f>
         <v>47605</v>
       </c>
-      <c r="H4" s="9">
-        <f t="shared" ref="H4:H35" si="7">H3+0.7</f>
+      <c r="J4" s="9">
+        <f t="shared" ref="J4:J35" si="7">J3+0.7</f>
         <v>47696.7</v>
       </c>
-      <c r="I4" s="9">
+      <c r="K4" s="9">
         <f t="shared" si="1"/>
         <v>47697.399999999994</v>
       </c>
-      <c r="J4" s="25">
-        <f t="shared" ref="J4:J57" si="8">H4+15</f>
+      <c r="L4" s="25">
+        <f t="shared" ref="L4:L57" si="8">J4+15</f>
         <v>47711.7</v>
       </c>
-      <c r="K4" s="25">
-        <f t="shared" ref="K4:K57" si="9">J4+1</f>
+      <c r="M4" s="25">
+        <f t="shared" ref="M4:M57" si="9">L4+1</f>
         <v>47712.7</v>
       </c>
-      <c r="L4" s="9">
-        <f t="shared" ref="L4:L35" si="10">L3+4</f>
+      <c r="N4" s="9">
+        <f t="shared" ref="N4:N35" si="10">N3+4</f>
         <v>47912</v>
       </c>
-      <c r="M4" s="9">
-        <f t="shared" ref="M4:M35" si="11">M3+4</f>
+      <c r="O4" s="9">
+        <f t="shared" ref="O4:O35" si="11">O3+4</f>
         <v>47916</v>
       </c>
-      <c r="N4" s="42">
-        <f t="shared" ref="N4:N57" si="12">L4+7</f>
+      <c r="P4" s="42">
+        <f t="shared" ref="P4:P57" si="12">N4+7</f>
         <v>47919</v>
       </c>
-      <c r="O4" s="42">
-        <f t="shared" ref="O4:O57" si="13">N4+5</f>
+      <c r="Q4" s="42">
+        <f t="shared" ref="Q4:Q57" si="13">P4+5</f>
         <v>47924</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -5896,54 +5928,62 @@
       </c>
       <c r="D5" s="25">
         <f t="shared" si="3"/>
-        <v>47546</v>
+        <v>47601</v>
       </c>
       <c r="E5" s="25">
         <f t="shared" si="4"/>
+        <v>47602</v>
+      </c>
+      <c r="F5" s="25">
+        <f>B5-30</f>
         <v>47546</v>
       </c>
-      <c r="F5" s="25">
+      <c r="G5" s="25">
         <f t="shared" si="5"/>
+        <v>47546</v>
+      </c>
+      <c r="H5" s="25">
+        <f>B5+30</f>
         <v>47606</v>
       </c>
-      <c r="G5" s="25">
+      <c r="I5" s="25">
         <f t="shared" si="6"/>
         <v>47606</v>
       </c>
-      <c r="H5" s="9">
+      <c r="J5" s="9">
         <f t="shared" si="7"/>
         <v>47697.399999999994</v>
       </c>
-      <c r="I5" s="9">
+      <c r="K5" s="9">
         <f t="shared" si="1"/>
         <v>47698.099999999991</v>
       </c>
-      <c r="J5" s="25">
+      <c r="L5" s="25">
         <f t="shared" si="8"/>
         <v>47712.399999999994</v>
       </c>
-      <c r="K5" s="25">
+      <c r="M5" s="25">
         <f t="shared" si="9"/>
         <v>47713.399999999994</v>
       </c>
-      <c r="L5" s="9">
+      <c r="N5" s="9">
         <f t="shared" si="10"/>
         <v>47916</v>
       </c>
-      <c r="M5" s="9">
+      <c r="O5" s="9">
         <f t="shared" si="11"/>
         <v>47920</v>
       </c>
-      <c r="N5" s="42">
+      <c r="P5" s="42">
         <f t="shared" si="12"/>
         <v>47923</v>
       </c>
-      <c r="O5" s="42">
+      <c r="Q5" s="42">
         <f t="shared" si="13"/>
         <v>47928</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -5957,54 +5997,62 @@
       </c>
       <c r="D6" s="25">
         <f t="shared" si="3"/>
-        <v>47547</v>
+        <v>47602</v>
       </c>
       <c r="E6" s="25">
         <f t="shared" si="4"/>
+        <v>47603</v>
+      </c>
+      <c r="F6" s="25">
+        <f>B6-30</f>
         <v>47547</v>
       </c>
-      <c r="F6" s="25">
+      <c r="G6" s="25">
         <f t="shared" si="5"/>
+        <v>47547</v>
+      </c>
+      <c r="H6" s="25">
+        <f>B6+30</f>
         <v>47607</v>
       </c>
-      <c r="G6" s="25">
+      <c r="I6" s="25">
         <f t="shared" si="6"/>
         <v>47607</v>
       </c>
-      <c r="H6" s="9">
+      <c r="J6" s="9">
         <f t="shared" si="7"/>
         <v>47698.099999999991</v>
       </c>
-      <c r="I6" s="9">
+      <c r="K6" s="9">
         <f t="shared" si="1"/>
         <v>47698.799999999988</v>
       </c>
-      <c r="J6" s="25">
+      <c r="L6" s="25">
         <f t="shared" si="8"/>
         <v>47713.099999999991</v>
       </c>
-      <c r="K6" s="25">
+      <c r="M6" s="25">
         <f t="shared" si="9"/>
         <v>47714.099999999991</v>
       </c>
-      <c r="L6" s="9">
+      <c r="N6" s="9">
         <f t="shared" si="10"/>
         <v>47920</v>
       </c>
-      <c r="M6" s="9">
+      <c r="O6" s="9">
         <f t="shared" si="11"/>
         <v>47924</v>
       </c>
-      <c r="N6" s="42">
+      <c r="P6" s="42">
         <f t="shared" si="12"/>
         <v>47927</v>
       </c>
-      <c r="O6" s="42">
+      <c r="Q6" s="42">
         <f t="shared" si="13"/>
         <v>47932</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -6018,54 +6066,62 @@
       </c>
       <c r="D7" s="25">
         <f t="shared" si="3"/>
-        <v>47548</v>
+        <v>47603</v>
       </c>
       <c r="E7" s="25">
         <f t="shared" si="4"/>
+        <v>47604</v>
+      </c>
+      <c r="F7" s="25">
+        <f>B7-30</f>
         <v>47548</v>
       </c>
-      <c r="F7" s="25">
+      <c r="G7" s="25">
         <f t="shared" si="5"/>
+        <v>47548</v>
+      </c>
+      <c r="H7" s="25">
+        <f>B7+30</f>
         <v>47608</v>
       </c>
-      <c r="G7" s="25">
+      <c r="I7" s="25">
         <f t="shared" si="6"/>
         <v>47608</v>
       </c>
-      <c r="H7" s="9">
+      <c r="J7" s="9">
         <f t="shared" si="7"/>
         <v>47698.799999999988</v>
       </c>
-      <c r="I7" s="9">
+      <c r="K7" s="9">
         <f t="shared" si="1"/>
         <v>47699.499999999985</v>
       </c>
-      <c r="J7" s="25">
+      <c r="L7" s="25">
         <f t="shared" si="8"/>
         <v>47713.799999999988</v>
       </c>
-      <c r="K7" s="25">
+      <c r="M7" s="25">
         <f t="shared" si="9"/>
         <v>47714.799999999988</v>
       </c>
-      <c r="L7" s="9">
+      <c r="N7" s="9">
         <f t="shared" si="10"/>
         <v>47924</v>
       </c>
-      <c r="M7" s="9">
+      <c r="O7" s="9">
         <f t="shared" si="11"/>
         <v>47928</v>
       </c>
-      <c r="N7" s="42">
+      <c r="P7" s="42">
         <f t="shared" si="12"/>
         <v>47931</v>
       </c>
-      <c r="O7" s="42">
+      <c r="Q7" s="42">
         <f t="shared" si="13"/>
         <v>47936</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -6079,54 +6135,62 @@
       </c>
       <c r="D8" s="25">
         <f t="shared" si="3"/>
-        <v>47549</v>
+        <v>47604</v>
       </c>
       <c r="E8" s="25">
         <f t="shared" si="4"/>
+        <v>47605</v>
+      </c>
+      <c r="F8" s="25">
+        <f>B8-30</f>
         <v>47549</v>
       </c>
-      <c r="F8" s="25">
+      <c r="G8" s="25">
         <f t="shared" si="5"/>
+        <v>47549</v>
+      </c>
+      <c r="H8" s="25">
+        <f>B8+30</f>
         <v>47609</v>
       </c>
-      <c r="G8" s="25">
+      <c r="I8" s="25">
         <f t="shared" si="6"/>
         <v>47609</v>
       </c>
-      <c r="H8" s="9">
+      <c r="J8" s="9">
         <f t="shared" si="7"/>
         <v>47699.499999999985</v>
       </c>
-      <c r="I8" s="9">
+      <c r="K8" s="9">
         <f t="shared" si="1"/>
         <v>47700.199999999983</v>
       </c>
-      <c r="J8" s="25">
+      <c r="L8" s="25">
         <f t="shared" si="8"/>
         <v>47714.499999999985</v>
       </c>
-      <c r="K8" s="25">
+      <c r="M8" s="25">
         <f t="shared" si="9"/>
         <v>47715.499999999985</v>
       </c>
-      <c r="L8" s="9">
+      <c r="N8" s="9">
         <f t="shared" si="10"/>
         <v>47928</v>
       </c>
-      <c r="M8" s="9">
+      <c r="O8" s="9">
         <f t="shared" si="11"/>
         <v>47932</v>
       </c>
-      <c r="N8" s="42">
+      <c r="P8" s="42">
         <f t="shared" si="12"/>
         <v>47935</v>
       </c>
-      <c r="O8" s="42">
+      <c r="Q8" s="42">
         <f t="shared" si="13"/>
         <v>47940</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -6140,54 +6204,62 @@
       </c>
       <c r="D9" s="25">
         <f t="shared" si="3"/>
-        <v>47550</v>
+        <v>47605</v>
       </c>
       <c r="E9" s="25">
         <f t="shared" si="4"/>
+        <v>47606</v>
+      </c>
+      <c r="F9" s="25">
+        <f>B9-30</f>
         <v>47550</v>
       </c>
-      <c r="F9" s="25">
+      <c r="G9" s="25">
         <f t="shared" si="5"/>
+        <v>47550</v>
+      </c>
+      <c r="H9" s="25">
+        <f>B9+30</f>
         <v>47610</v>
       </c>
-      <c r="G9" s="25">
+      <c r="I9" s="25">
         <f t="shared" si="6"/>
         <v>47610</v>
       </c>
-      <c r="H9" s="9">
+      <c r="J9" s="9">
         <f t="shared" si="7"/>
         <v>47700.199999999983</v>
       </c>
-      <c r="I9" s="9">
+      <c r="K9" s="9">
         <f t="shared" si="1"/>
         <v>47700.89999999998</v>
       </c>
-      <c r="J9" s="25">
+      <c r="L9" s="25">
         <f t="shared" si="8"/>
         <v>47715.199999999983</v>
       </c>
-      <c r="K9" s="25">
+      <c r="M9" s="25">
         <f t="shared" si="9"/>
         <v>47716.199999999983</v>
       </c>
-      <c r="L9" s="9">
+      <c r="N9" s="9">
         <f t="shared" si="10"/>
         <v>47932</v>
       </c>
-      <c r="M9" s="9">
+      <c r="O9" s="9">
         <f t="shared" si="11"/>
         <v>47936</v>
       </c>
-      <c r="N9" s="42">
+      <c r="P9" s="42">
         <f t="shared" si="12"/>
         <v>47939</v>
       </c>
-      <c r="O9" s="42">
+      <c r="Q9" s="42">
         <f t="shared" si="13"/>
         <v>47944</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -6201,54 +6273,62 @@
       </c>
       <c r="D10" s="25">
         <f t="shared" si="3"/>
-        <v>47551</v>
+        <v>47606</v>
       </c>
       <c r="E10" s="25">
         <f t="shared" si="4"/>
+        <v>47607</v>
+      </c>
+      <c r="F10" s="25">
+        <f>B10-30</f>
         <v>47551</v>
       </c>
-      <c r="F10" s="25">
+      <c r="G10" s="25">
         <f t="shared" si="5"/>
+        <v>47551</v>
+      </c>
+      <c r="H10" s="25">
+        <f>B10+30</f>
         <v>47611</v>
       </c>
-      <c r="G10" s="25">
+      <c r="I10" s="25">
         <f t="shared" si="6"/>
         <v>47611</v>
       </c>
-      <c r="H10" s="9">
+      <c r="J10" s="9">
         <f t="shared" si="7"/>
         <v>47700.89999999998</v>
       </c>
-      <c r="I10" s="9">
+      <c r="K10" s="9">
         <f t="shared" si="1"/>
         <v>47701.599999999977</v>
       </c>
-      <c r="J10" s="25">
+      <c r="L10" s="25">
         <f t="shared" si="8"/>
         <v>47715.89999999998</v>
       </c>
-      <c r="K10" s="25">
+      <c r="M10" s="25">
         <f t="shared" si="9"/>
         <v>47716.89999999998</v>
       </c>
-      <c r="L10" s="9">
+      <c r="N10" s="9">
         <f t="shared" si="10"/>
         <v>47936</v>
       </c>
-      <c r="M10" s="9">
+      <c r="O10" s="9">
         <f t="shared" si="11"/>
         <v>47940</v>
       </c>
-      <c r="N10" s="42">
+      <c r="P10" s="42">
         <f t="shared" si="12"/>
         <v>47943</v>
       </c>
-      <c r="O10" s="42">
+      <c r="Q10" s="42">
         <f t="shared" si="13"/>
         <v>47948</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -6262,54 +6342,62 @@
       </c>
       <c r="D11" s="25">
         <f t="shared" si="3"/>
-        <v>47552</v>
+        <v>47607</v>
       </c>
       <c r="E11" s="25">
         <f t="shared" si="4"/>
+        <v>47608</v>
+      </c>
+      <c r="F11" s="25">
+        <f>B11-30</f>
         <v>47552</v>
       </c>
-      <c r="F11" s="25">
+      <c r="G11" s="25">
         <f t="shared" si="5"/>
+        <v>47552</v>
+      </c>
+      <c r="H11" s="25">
+        <f>B11+30</f>
         <v>47612</v>
       </c>
-      <c r="G11" s="25">
+      <c r="I11" s="25">
         <f t="shared" si="6"/>
         <v>47612</v>
       </c>
-      <c r="H11" s="9">
+      <c r="J11" s="9">
         <f t="shared" si="7"/>
         <v>47701.599999999977</v>
       </c>
-      <c r="I11" s="9">
+      <c r="K11" s="9">
         <f t="shared" si="1"/>
         <v>47702.299999999974</v>
       </c>
-      <c r="J11" s="25">
+      <c r="L11" s="25">
         <f t="shared" si="8"/>
         <v>47716.599999999977</v>
       </c>
-      <c r="K11" s="25">
+      <c r="M11" s="25">
         <f t="shared" si="9"/>
         <v>47717.599999999977</v>
       </c>
-      <c r="L11" s="9">
+      <c r="N11" s="9">
         <f t="shared" si="10"/>
         <v>47940</v>
       </c>
-      <c r="M11" s="9">
+      <c r="O11" s="9">
         <f t="shared" si="11"/>
         <v>47944</v>
       </c>
-      <c r="N11" s="42">
+      <c r="P11" s="42">
         <f t="shared" si="12"/>
         <v>47947</v>
       </c>
-      <c r="O11" s="42">
+      <c r="Q11" s="42">
         <f t="shared" si="13"/>
         <v>47952</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -6323,54 +6411,62 @@
       </c>
       <c r="D12" s="25">
         <f t="shared" si="3"/>
-        <v>47553</v>
+        <v>47608</v>
       </c>
       <c r="E12" s="25">
         <f t="shared" si="4"/>
+        <v>47609</v>
+      </c>
+      <c r="F12" s="25">
+        <f>B12-30</f>
         <v>47553</v>
       </c>
-      <c r="F12" s="25">
+      <c r="G12" s="25">
         <f t="shared" si="5"/>
+        <v>47553</v>
+      </c>
+      <c r="H12" s="25">
+        <f>B12+30</f>
         <v>47613</v>
       </c>
-      <c r="G12" s="25">
+      <c r="I12" s="25">
         <f t="shared" si="6"/>
         <v>47613</v>
       </c>
-      <c r="H12" s="9">
+      <c r="J12" s="9">
         <f t="shared" si="7"/>
         <v>47702.299999999974</v>
       </c>
-      <c r="I12" s="9">
+      <c r="K12" s="9">
         <f t="shared" si="1"/>
         <v>47702.999999999971</v>
       </c>
-      <c r="J12" s="25">
+      <c r="L12" s="25">
         <f t="shared" si="8"/>
         <v>47717.299999999974</v>
       </c>
-      <c r="K12" s="25">
+      <c r="M12" s="25">
         <f t="shared" si="9"/>
         <v>47718.299999999974</v>
       </c>
-      <c r="L12" s="9">
+      <c r="N12" s="9">
         <f t="shared" si="10"/>
         <v>47944</v>
       </c>
-      <c r="M12" s="9">
+      <c r="O12" s="9">
         <f t="shared" si="11"/>
         <v>47948</v>
       </c>
-      <c r="N12" s="42">
+      <c r="P12" s="42">
         <f t="shared" si="12"/>
         <v>47951</v>
       </c>
-      <c r="O12" s="42">
+      <c r="Q12" s="42">
         <f t="shared" si="13"/>
         <v>47956</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -6384,54 +6480,62 @@
       </c>
       <c r="D13" s="25">
         <f t="shared" si="3"/>
-        <v>47554</v>
+        <v>47609</v>
       </c>
       <c r="E13" s="25">
         <f t="shared" si="4"/>
+        <v>47610</v>
+      </c>
+      <c r="F13" s="25">
+        <f>B13-30</f>
         <v>47554</v>
       </c>
-      <c r="F13" s="25">
+      <c r="G13" s="25">
         <f t="shared" si="5"/>
+        <v>47554</v>
+      </c>
+      <c r="H13" s="25">
+        <f>B13+30</f>
         <v>47614</v>
       </c>
-      <c r="G13" s="25">
+      <c r="I13" s="25">
         <f t="shared" si="6"/>
         <v>47614</v>
       </c>
-      <c r="H13" s="9">
+      <c r="J13" s="9">
         <f t="shared" si="7"/>
         <v>47702.999999999971</v>
       </c>
-      <c r="I13" s="9">
+      <c r="K13" s="9">
         <f t="shared" si="1"/>
         <v>47703.699999999968</v>
       </c>
-      <c r="J13" s="25">
+      <c r="L13" s="25">
         <f t="shared" si="8"/>
         <v>47717.999999999971</v>
       </c>
-      <c r="K13" s="25">
+      <c r="M13" s="25">
         <f t="shared" si="9"/>
         <v>47718.999999999971</v>
       </c>
-      <c r="L13" s="9">
+      <c r="N13" s="9">
         <f t="shared" si="10"/>
         <v>47948</v>
       </c>
-      <c r="M13" s="9">
+      <c r="O13" s="9">
         <f t="shared" si="11"/>
         <v>47952</v>
       </c>
-      <c r="N13" s="42">
+      <c r="P13" s="42">
         <f t="shared" si="12"/>
         <v>47955</v>
       </c>
-      <c r="O13" s="42">
+      <c r="Q13" s="42">
         <f t="shared" si="13"/>
         <v>47960</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -6445,54 +6549,62 @@
       </c>
       <c r="D14" s="25">
         <f t="shared" si="3"/>
-        <v>47555</v>
+        <v>47610</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="4"/>
+        <v>47611</v>
+      </c>
+      <c r="F14" s="25">
+        <f>B14-30</f>
         <v>47555</v>
       </c>
-      <c r="F14" s="25">
+      <c r="G14" s="25">
         <f t="shared" si="5"/>
+        <v>47555</v>
+      </c>
+      <c r="H14" s="25">
+        <f>B14+30</f>
         <v>47615</v>
       </c>
-      <c r="G14" s="25">
+      <c r="I14" s="25">
         <f t="shared" si="6"/>
         <v>47615</v>
       </c>
-      <c r="H14" s="9">
+      <c r="J14" s="9">
         <f t="shared" si="7"/>
         <v>47703.699999999968</v>
       </c>
-      <c r="I14" s="9">
+      <c r="K14" s="9">
         <f t="shared" si="1"/>
         <v>47704.399999999965</v>
       </c>
-      <c r="J14" s="25">
+      <c r="L14" s="25">
         <f t="shared" si="8"/>
         <v>47718.699999999968</v>
       </c>
-      <c r="K14" s="25">
+      <c r="M14" s="25">
         <f t="shared" si="9"/>
         <v>47719.699999999968</v>
       </c>
-      <c r="L14" s="9">
+      <c r="N14" s="9">
         <f t="shared" si="10"/>
         <v>47952</v>
       </c>
-      <c r="M14" s="9">
+      <c r="O14" s="9">
         <f t="shared" si="11"/>
         <v>47956</v>
       </c>
-      <c r="N14" s="42">
+      <c r="P14" s="42">
         <f t="shared" si="12"/>
         <v>47959</v>
       </c>
-      <c r="O14" s="42">
+      <c r="Q14" s="42">
         <f t="shared" si="13"/>
         <v>47964</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -6506,54 +6618,62 @@
       </c>
       <c r="D15" s="25">
         <f t="shared" si="3"/>
-        <v>47556</v>
+        <v>47611</v>
       </c>
       <c r="E15" s="25">
         <f t="shared" si="4"/>
+        <v>47612</v>
+      </c>
+      <c r="F15" s="25">
+        <f>B15-30</f>
         <v>47556</v>
       </c>
-      <c r="F15" s="25">
+      <c r="G15" s="25">
         <f t="shared" si="5"/>
+        <v>47556</v>
+      </c>
+      <c r="H15" s="25">
+        <f>B15+30</f>
         <v>47616</v>
       </c>
-      <c r="G15" s="25">
+      <c r="I15" s="25">
         <f t="shared" si="6"/>
         <v>47616</v>
       </c>
-      <c r="H15" s="9">
+      <c r="J15" s="9">
         <f t="shared" si="7"/>
         <v>47704.399999999965</v>
       </c>
-      <c r="I15" s="9">
+      <c r="K15" s="9">
         <f t="shared" si="1"/>
         <v>47705.099999999962</v>
       </c>
-      <c r="J15" s="25">
+      <c r="L15" s="25">
         <f t="shared" si="8"/>
         <v>47719.399999999965</v>
       </c>
-      <c r="K15" s="25">
+      <c r="M15" s="25">
         <f t="shared" si="9"/>
         <v>47720.399999999965</v>
       </c>
-      <c r="L15" s="9">
+      <c r="N15" s="9">
         <f t="shared" si="10"/>
         <v>47956</v>
       </c>
-      <c r="M15" s="9">
+      <c r="O15" s="9">
         <f t="shared" si="11"/>
         <v>47960</v>
       </c>
-      <c r="N15" s="42">
+      <c r="P15" s="42">
         <f t="shared" si="12"/>
         <v>47963</v>
       </c>
-      <c r="O15" s="42">
+      <c r="Q15" s="42">
         <f t="shared" si="13"/>
         <v>47968</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -6567,54 +6687,62 @@
       </c>
       <c r="D16" s="25">
         <f t="shared" si="3"/>
-        <v>47557</v>
+        <v>47612</v>
       </c>
       <c r="E16" s="25">
         <f t="shared" si="4"/>
+        <v>47613</v>
+      </c>
+      <c r="F16" s="25">
+        <f>B16-30</f>
         <v>47557</v>
       </c>
-      <c r="F16" s="25">
+      <c r="G16" s="25">
         <f t="shared" si="5"/>
+        <v>47557</v>
+      </c>
+      <c r="H16" s="25">
+        <f>B16+30</f>
         <v>47617</v>
       </c>
-      <c r="G16" s="25">
+      <c r="I16" s="25">
         <f t="shared" si="6"/>
         <v>47617</v>
       </c>
-      <c r="H16" s="9">
+      <c r="J16" s="9">
         <f t="shared" si="7"/>
         <v>47705.099999999962</v>
       </c>
-      <c r="I16" s="9">
+      <c r="K16" s="9">
         <f t="shared" si="1"/>
         <v>47705.799999999959</v>
       </c>
-      <c r="J16" s="25">
+      <c r="L16" s="25">
         <f t="shared" si="8"/>
         <v>47720.099999999962</v>
       </c>
-      <c r="K16" s="25">
+      <c r="M16" s="25">
         <f t="shared" si="9"/>
         <v>47721.099999999962</v>
       </c>
-      <c r="L16" s="9">
+      <c r="N16" s="9">
         <f t="shared" si="10"/>
         <v>47960</v>
       </c>
-      <c r="M16" s="9">
+      <c r="O16" s="9">
         <f t="shared" si="11"/>
         <v>47964</v>
       </c>
-      <c r="N16" s="42">
+      <c r="P16" s="42">
         <f t="shared" si="12"/>
         <v>47967</v>
       </c>
-      <c r="O16" s="42">
+      <c r="Q16" s="42">
         <f t="shared" si="13"/>
         <v>47972</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -6628,54 +6756,62 @@
       </c>
       <c r="D17" s="25">
         <f t="shared" si="3"/>
-        <v>47558</v>
+        <v>47613</v>
       </c>
       <c r="E17" s="25">
         <f t="shared" si="4"/>
+        <v>47614</v>
+      </c>
+      <c r="F17" s="25">
+        <f>B17-30</f>
         <v>47558</v>
       </c>
-      <c r="F17" s="25">
+      <c r="G17" s="25">
         <f t="shared" si="5"/>
+        <v>47558</v>
+      </c>
+      <c r="H17" s="25">
+        <f>B17+30</f>
         <v>47618</v>
       </c>
-      <c r="G17" s="25">
+      <c r="I17" s="25">
         <f t="shared" si="6"/>
         <v>47618</v>
       </c>
-      <c r="H17" s="9">
+      <c r="J17" s="9">
         <f t="shared" si="7"/>
         <v>47705.799999999959</v>
       </c>
-      <c r="I17" s="9">
+      <c r="K17" s="9">
         <f t="shared" si="1"/>
         <v>47706.499999999956</v>
       </c>
-      <c r="J17" s="25">
+      <c r="L17" s="25">
         <f t="shared" si="8"/>
         <v>47720.799999999959</v>
       </c>
-      <c r="K17" s="25">
+      <c r="M17" s="25">
         <f t="shared" si="9"/>
         <v>47721.799999999959</v>
       </c>
-      <c r="L17" s="9">
+      <c r="N17" s="9">
         <f t="shared" si="10"/>
         <v>47964</v>
       </c>
-      <c r="M17" s="9">
+      <c r="O17" s="9">
         <f t="shared" si="11"/>
         <v>47968</v>
       </c>
-      <c r="N17" s="42">
+      <c r="P17" s="42">
         <f t="shared" si="12"/>
         <v>47971</v>
       </c>
-      <c r="O17" s="42">
+      <c r="Q17" s="42">
         <f t="shared" si="13"/>
         <v>47976</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -6689,54 +6825,62 @@
       </c>
       <c r="D18" s="25">
         <f t="shared" si="3"/>
-        <v>47559</v>
+        <v>47614</v>
       </c>
       <c r="E18" s="25">
         <f t="shared" si="4"/>
+        <v>47615</v>
+      </c>
+      <c r="F18" s="25">
+        <f>B18-30</f>
         <v>47559</v>
       </c>
-      <c r="F18" s="25">
+      <c r="G18" s="25">
         <f t="shared" si="5"/>
+        <v>47559</v>
+      </c>
+      <c r="H18" s="25">
+        <f>B18+30</f>
         <v>47619</v>
       </c>
-      <c r="G18" s="25">
+      <c r="I18" s="25">
         <f t="shared" si="6"/>
         <v>47619</v>
       </c>
-      <c r="H18" s="9">
+      <c r="J18" s="9">
         <f t="shared" si="7"/>
         <v>47706.499999999956</v>
       </c>
-      <c r="I18" s="9">
+      <c r="K18" s="9">
         <f t="shared" si="1"/>
         <v>47707.199999999953</v>
       </c>
-      <c r="J18" s="25">
+      <c r="L18" s="25">
         <f t="shared" si="8"/>
         <v>47721.499999999956</v>
       </c>
-      <c r="K18" s="25">
+      <c r="M18" s="25">
         <f t="shared" si="9"/>
         <v>47722.499999999956</v>
       </c>
-      <c r="L18" s="9">
+      <c r="N18" s="9">
         <f t="shared" si="10"/>
         <v>47968</v>
       </c>
-      <c r="M18" s="9">
+      <c r="O18" s="9">
         <f t="shared" si="11"/>
         <v>47972</v>
       </c>
-      <c r="N18" s="42">
+      <c r="P18" s="42">
         <f t="shared" si="12"/>
         <v>47975</v>
       </c>
-      <c r="O18" s="42">
+      <c r="Q18" s="42">
         <f t="shared" si="13"/>
         <v>47980</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -6750,54 +6894,62 @@
       </c>
       <c r="D19" s="25">
         <f t="shared" si="3"/>
-        <v>47560</v>
+        <v>47615</v>
       </c>
       <c r="E19" s="25">
         <f t="shared" si="4"/>
+        <v>47616</v>
+      </c>
+      <c r="F19" s="25">
+        <f>B19-30</f>
         <v>47560</v>
       </c>
-      <c r="F19" s="25">
+      <c r="G19" s="25">
         <f t="shared" si="5"/>
+        <v>47560</v>
+      </c>
+      <c r="H19" s="25">
+        <f>B19+30</f>
         <v>47620</v>
       </c>
-      <c r="G19" s="25">
+      <c r="I19" s="25">
         <f t="shared" si="6"/>
         <v>47620</v>
       </c>
-      <c r="H19" s="9">
+      <c r="J19" s="9">
         <f t="shared" si="7"/>
         <v>47707.199999999953</v>
       </c>
-      <c r="I19" s="9">
+      <c r="K19" s="9">
         <f t="shared" si="1"/>
         <v>47707.899999999951</v>
       </c>
-      <c r="J19" s="25">
+      <c r="L19" s="25">
         <f t="shared" si="8"/>
         <v>47722.199999999953</v>
       </c>
-      <c r="K19" s="25">
+      <c r="M19" s="25">
         <f t="shared" si="9"/>
         <v>47723.199999999953</v>
       </c>
-      <c r="L19" s="9">
+      <c r="N19" s="9">
         <f t="shared" si="10"/>
         <v>47972</v>
       </c>
-      <c r="M19" s="9">
+      <c r="O19" s="9">
         <f t="shared" si="11"/>
         <v>47976</v>
       </c>
-      <c r="N19" s="42">
+      <c r="P19" s="42">
         <f t="shared" si="12"/>
         <v>47979</v>
       </c>
-      <c r="O19" s="42">
+      <c r="Q19" s="42">
         <f t="shared" si="13"/>
         <v>47984</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>18</v>
       </c>
@@ -6811,54 +6963,62 @@
       </c>
       <c r="D20" s="25">
         <f t="shared" si="3"/>
-        <v>47561</v>
+        <v>47616</v>
       </c>
       <c r="E20" s="25">
         <f t="shared" si="4"/>
+        <v>47617</v>
+      </c>
+      <c r="F20" s="25">
+        <f>B20-30</f>
         <v>47561</v>
       </c>
-      <c r="F20" s="25">
+      <c r="G20" s="25">
         <f t="shared" si="5"/>
+        <v>47561</v>
+      </c>
+      <c r="H20" s="25">
+        <f>B20+30</f>
         <v>47621</v>
       </c>
-      <c r="G20" s="25">
+      <c r="I20" s="25">
         <f t="shared" si="6"/>
         <v>47621</v>
       </c>
-      <c r="H20" s="9">
+      <c r="J20" s="9">
         <f t="shared" si="7"/>
         <v>47707.899999999951</v>
       </c>
-      <c r="I20" s="9">
+      <c r="K20" s="9">
         <f t="shared" si="1"/>
         <v>47708.599999999948</v>
       </c>
-      <c r="J20" s="25">
+      <c r="L20" s="25">
         <f t="shared" si="8"/>
         <v>47722.899999999951</v>
       </c>
-      <c r="K20" s="25">
+      <c r="M20" s="25">
         <f t="shared" si="9"/>
         <v>47723.899999999951</v>
       </c>
-      <c r="L20" s="9">
+      <c r="N20" s="9">
         <f t="shared" si="10"/>
         <v>47976</v>
       </c>
-      <c r="M20" s="9">
+      <c r="O20" s="9">
         <f t="shared" si="11"/>
         <v>47980</v>
       </c>
-      <c r="N20" s="42">
+      <c r="P20" s="42">
         <f t="shared" si="12"/>
         <v>47983</v>
       </c>
-      <c r="O20" s="42">
+      <c r="Q20" s="42">
         <f t="shared" si="13"/>
         <v>47988</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>19</v>
       </c>
@@ -6872,54 +7032,62 @@
       </c>
       <c r="D21" s="25">
         <f t="shared" si="3"/>
-        <v>47562</v>
+        <v>47617</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="4"/>
+        <v>47618</v>
+      </c>
+      <c r="F21" s="25">
+        <f>B21-30</f>
         <v>47562</v>
       </c>
-      <c r="F21" s="25">
+      <c r="G21" s="25">
         <f t="shared" si="5"/>
+        <v>47562</v>
+      </c>
+      <c r="H21" s="25">
+        <f>B21+30</f>
         <v>47622</v>
       </c>
-      <c r="G21" s="25">
+      <c r="I21" s="25">
         <f t="shared" si="6"/>
         <v>47622</v>
       </c>
-      <c r="H21" s="9">
+      <c r="J21" s="9">
         <f t="shared" si="7"/>
         <v>47708.599999999948</v>
       </c>
-      <c r="I21" s="9">
+      <c r="K21" s="9">
         <f t="shared" si="1"/>
         <v>47709.299999999945</v>
       </c>
-      <c r="J21" s="25">
+      <c r="L21" s="25">
         <f t="shared" si="8"/>
         <v>47723.599999999948</v>
       </c>
-      <c r="K21" s="25">
+      <c r="M21" s="25">
         <f t="shared" si="9"/>
         <v>47724.599999999948</v>
       </c>
-      <c r="L21" s="9">
+      <c r="N21" s="9">
         <f t="shared" si="10"/>
         <v>47980</v>
       </c>
-      <c r="M21" s="9">
+      <c r="O21" s="9">
         <f t="shared" si="11"/>
         <v>47984</v>
       </c>
-      <c r="N21" s="42">
+      <c r="P21" s="42">
         <f t="shared" si="12"/>
         <v>47987</v>
       </c>
-      <c r="O21" s="42">
+      <c r="Q21" s="42">
         <f t="shared" si="13"/>
         <v>47992</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>20</v>
       </c>
@@ -6933,54 +7101,62 @@
       </c>
       <c r="D22" s="25">
         <f t="shared" si="3"/>
-        <v>47563</v>
+        <v>47618</v>
       </c>
       <c r="E22" s="25">
         <f t="shared" si="4"/>
+        <v>47619</v>
+      </c>
+      <c r="F22" s="25">
+        <f>B22-30</f>
         <v>47563</v>
       </c>
-      <c r="F22" s="25">
+      <c r="G22" s="25">
         <f t="shared" si="5"/>
+        <v>47563</v>
+      </c>
+      <c r="H22" s="25">
+        <f>B22+30</f>
         <v>47623</v>
       </c>
-      <c r="G22" s="25">
+      <c r="I22" s="25">
         <f t="shared" si="6"/>
         <v>47623</v>
       </c>
-      <c r="H22" s="9">
+      <c r="J22" s="9">
         <f t="shared" si="7"/>
         <v>47709.299999999945</v>
       </c>
-      <c r="I22" s="9">
+      <c r="K22" s="9">
         <f t="shared" si="1"/>
         <v>47709.999999999942</v>
       </c>
-      <c r="J22" s="25">
+      <c r="L22" s="25">
         <f t="shared" si="8"/>
         <v>47724.299999999945</v>
       </c>
-      <c r="K22" s="25">
+      <c r="M22" s="25">
         <f t="shared" si="9"/>
         <v>47725.299999999945</v>
       </c>
-      <c r="L22" s="9">
+      <c r="N22" s="9">
         <f t="shared" si="10"/>
         <v>47984</v>
       </c>
-      <c r="M22" s="9">
+      <c r="O22" s="9">
         <f t="shared" si="11"/>
         <v>47988</v>
       </c>
-      <c r="N22" s="42">
+      <c r="P22" s="42">
         <f t="shared" si="12"/>
         <v>47991</v>
       </c>
-      <c r="O22" s="42">
+      <c r="Q22" s="42">
         <f t="shared" si="13"/>
         <v>47996</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>21</v>
       </c>
@@ -6994,54 +7170,62 @@
       </c>
       <c r="D23" s="25">
         <f t="shared" si="3"/>
-        <v>47564</v>
+        <v>47619</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="4"/>
+        <v>47620</v>
+      </c>
+      <c r="F23" s="25">
+        <f>B23-30</f>
         <v>47564</v>
       </c>
-      <c r="F23" s="25">
+      <c r="G23" s="25">
         <f t="shared" si="5"/>
+        <v>47564</v>
+      </c>
+      <c r="H23" s="25">
+        <f>B23+30</f>
         <v>47624</v>
       </c>
-      <c r="G23" s="25">
+      <c r="I23" s="25">
         <f t="shared" si="6"/>
         <v>47624</v>
       </c>
-      <c r="H23" s="9">
+      <c r="J23" s="9">
         <f t="shared" si="7"/>
         <v>47709.999999999942</v>
       </c>
-      <c r="I23" s="9">
+      <c r="K23" s="9">
         <f t="shared" si="1"/>
         <v>47710.699999999939</v>
       </c>
-      <c r="J23" s="25">
+      <c r="L23" s="25">
         <f t="shared" si="8"/>
         <v>47724.999999999942</v>
       </c>
-      <c r="K23" s="25">
+      <c r="M23" s="25">
         <f t="shared" si="9"/>
         <v>47725.999999999942</v>
       </c>
-      <c r="L23" s="9">
+      <c r="N23" s="9">
         <f t="shared" si="10"/>
         <v>47988</v>
       </c>
-      <c r="M23" s="9">
+      <c r="O23" s="9">
         <f t="shared" si="11"/>
         <v>47992</v>
       </c>
-      <c r="N23" s="42">
+      <c r="P23" s="42">
         <f t="shared" si="12"/>
         <v>47995</v>
       </c>
-      <c r="O23" s="42">
+      <c r="Q23" s="42">
         <f t="shared" si="13"/>
         <v>48000</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>22</v>
       </c>
@@ -7055,54 +7239,62 @@
       </c>
       <c r="D24" s="25">
         <f t="shared" si="3"/>
-        <v>47565</v>
+        <v>47620</v>
       </c>
       <c r="E24" s="25">
         <f t="shared" si="4"/>
+        <v>47621</v>
+      </c>
+      <c r="F24" s="25">
+        <f>B24-30</f>
         <v>47565</v>
       </c>
-      <c r="F24" s="25">
+      <c r="G24" s="25">
         <f t="shared" si="5"/>
+        <v>47565</v>
+      </c>
+      <c r="H24" s="25">
+        <f>B24+30</f>
         <v>47625</v>
       </c>
-      <c r="G24" s="25">
+      <c r="I24" s="25">
         <f t="shared" si="6"/>
         <v>47625</v>
       </c>
-      <c r="H24" s="9">
+      <c r="J24" s="9">
         <f t="shared" si="7"/>
         <v>47710.699999999939</v>
       </c>
-      <c r="I24" s="9">
+      <c r="K24" s="9">
         <f t="shared" si="1"/>
         <v>47711.399999999936</v>
       </c>
-      <c r="J24" s="25">
+      <c r="L24" s="25">
         <f t="shared" si="8"/>
         <v>47725.699999999939</v>
       </c>
-      <c r="K24" s="25">
+      <c r="M24" s="25">
         <f t="shared" si="9"/>
         <v>47726.699999999939</v>
       </c>
-      <c r="L24" s="9">
+      <c r="N24" s="9">
         <f t="shared" si="10"/>
         <v>47992</v>
       </c>
-      <c r="M24" s="9">
+      <c r="O24" s="9">
         <f t="shared" si="11"/>
         <v>47996</v>
       </c>
-      <c r="N24" s="42">
+      <c r="P24" s="42">
         <f t="shared" si="12"/>
         <v>47999</v>
       </c>
-      <c r="O24" s="42">
+      <c r="Q24" s="42">
         <f t="shared" si="13"/>
         <v>48004</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>23</v>
       </c>
@@ -7116,54 +7308,62 @@
       </c>
       <c r="D25" s="25">
         <f t="shared" si="3"/>
-        <v>47566</v>
+        <v>47621</v>
       </c>
       <c r="E25" s="25">
         <f t="shared" si="4"/>
+        <v>47622</v>
+      </c>
+      <c r="F25" s="25">
+        <f>B25-30</f>
         <v>47566</v>
       </c>
-      <c r="F25" s="25">
+      <c r="G25" s="25">
         <f t="shared" si="5"/>
+        <v>47566</v>
+      </c>
+      <c r="H25" s="25">
+        <f>B25+30</f>
         <v>47626</v>
       </c>
-      <c r="G25" s="25">
+      <c r="I25" s="25">
         <f t="shared" si="6"/>
         <v>47626</v>
       </c>
-      <c r="H25" s="9">
+      <c r="J25" s="9">
         <f t="shared" si="7"/>
         <v>47711.399999999936</v>
       </c>
-      <c r="I25" s="9">
+      <c r="K25" s="9">
         <f t="shared" si="1"/>
         <v>47712.099999999933</v>
       </c>
-      <c r="J25" s="25">
+      <c r="L25" s="25">
         <f t="shared" si="8"/>
         <v>47726.399999999936</v>
       </c>
-      <c r="K25" s="25">
+      <c r="M25" s="25">
         <f t="shared" si="9"/>
         <v>47727.399999999936</v>
       </c>
-      <c r="L25" s="9">
+      <c r="N25" s="9">
         <f t="shared" si="10"/>
         <v>47996</v>
       </c>
-      <c r="M25" s="9">
+      <c r="O25" s="9">
         <f t="shared" si="11"/>
         <v>48000</v>
       </c>
-      <c r="N25" s="42">
+      <c r="P25" s="42">
         <f t="shared" si="12"/>
         <v>48003</v>
       </c>
-      <c r="O25" s="42">
+      <c r="Q25" s="42">
         <f t="shared" si="13"/>
         <v>48008</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>24</v>
       </c>
@@ -7177,54 +7377,62 @@
       </c>
       <c r="D26" s="25">
         <f t="shared" si="3"/>
-        <v>47567</v>
+        <v>47622</v>
       </c>
       <c r="E26" s="25">
         <f t="shared" si="4"/>
+        <v>47623</v>
+      </c>
+      <c r="F26" s="25">
+        <f>B26-30</f>
         <v>47567</v>
       </c>
-      <c r="F26" s="25">
+      <c r="G26" s="25">
         <f t="shared" si="5"/>
+        <v>47567</v>
+      </c>
+      <c r="H26" s="25">
+        <f>B26+30</f>
         <v>47627</v>
       </c>
-      <c r="G26" s="25">
+      <c r="I26" s="25">
         <f t="shared" si="6"/>
         <v>47627</v>
       </c>
-      <c r="H26" s="9">
+      <c r="J26" s="9">
         <f t="shared" si="7"/>
         <v>47712.099999999933</v>
       </c>
-      <c r="I26" s="9">
+      <c r="K26" s="9">
         <f t="shared" si="1"/>
         <v>47712.79999999993</v>
       </c>
-      <c r="J26" s="25">
+      <c r="L26" s="25">
         <f t="shared" si="8"/>
         <v>47727.099999999933</v>
       </c>
-      <c r="K26" s="25">
+      <c r="M26" s="25">
         <f t="shared" si="9"/>
         <v>47728.099999999933</v>
       </c>
-      <c r="L26" s="9">
+      <c r="N26" s="9">
         <f t="shared" si="10"/>
         <v>48000</v>
       </c>
-      <c r="M26" s="9">
+      <c r="O26" s="9">
         <f t="shared" si="11"/>
         <v>48004</v>
       </c>
-      <c r="N26" s="42">
+      <c r="P26" s="42">
         <f t="shared" si="12"/>
         <v>48007</v>
       </c>
-      <c r="O26" s="42">
+      <c r="Q26" s="42">
         <f t="shared" si="13"/>
         <v>48012</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>25</v>
       </c>
@@ -7238,54 +7446,62 @@
       </c>
       <c r="D27" s="25">
         <f t="shared" si="3"/>
-        <v>47568</v>
+        <v>47623</v>
       </c>
       <c r="E27" s="25">
         <f t="shared" si="4"/>
+        <v>47624</v>
+      </c>
+      <c r="F27" s="25">
+        <f>B27-30</f>
         <v>47568</v>
       </c>
-      <c r="F27" s="25">
+      <c r="G27" s="25">
         <f t="shared" si="5"/>
+        <v>47568</v>
+      </c>
+      <c r="H27" s="25">
+        <f>B27+30</f>
         <v>47628</v>
       </c>
-      <c r="G27" s="25">
+      <c r="I27" s="25">
         <f t="shared" si="6"/>
         <v>47628</v>
       </c>
-      <c r="H27" s="9">
+      <c r="J27" s="9">
         <f t="shared" si="7"/>
         <v>47712.79999999993</v>
       </c>
-      <c r="I27" s="9">
+      <c r="K27" s="9">
         <f t="shared" si="1"/>
         <v>47713.499999999927</v>
       </c>
-      <c r="J27" s="25">
+      <c r="L27" s="25">
         <f t="shared" si="8"/>
         <v>47727.79999999993</v>
       </c>
-      <c r="K27" s="25">
+      <c r="M27" s="25">
         <f t="shared" si="9"/>
         <v>47728.79999999993</v>
       </c>
-      <c r="L27" s="9">
+      <c r="N27" s="9">
         <f t="shared" si="10"/>
         <v>48004</v>
       </c>
-      <c r="M27" s="9">
+      <c r="O27" s="9">
         <f t="shared" si="11"/>
         <v>48008</v>
       </c>
-      <c r="N27" s="42">
+      <c r="P27" s="42">
         <f t="shared" si="12"/>
         <v>48011</v>
       </c>
-      <c r="O27" s="42">
+      <c r="Q27" s="42">
         <f t="shared" si="13"/>
         <v>48016</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>26</v>
       </c>
@@ -7299,54 +7515,62 @@
       </c>
       <c r="D28" s="25">
         <f t="shared" si="3"/>
-        <v>47569</v>
+        <v>47624</v>
       </c>
       <c r="E28" s="25">
         <f t="shared" si="4"/>
+        <v>47625</v>
+      </c>
+      <c r="F28" s="25">
+        <f>B28-30</f>
         <v>47569</v>
       </c>
-      <c r="F28" s="25">
+      <c r="G28" s="25">
         <f t="shared" si="5"/>
+        <v>47569</v>
+      </c>
+      <c r="H28" s="25">
+        <f>B28+30</f>
         <v>47629</v>
       </c>
-      <c r="G28" s="25">
+      <c r="I28" s="25">
         <f t="shared" si="6"/>
         <v>47629</v>
       </c>
-      <c r="H28" s="9">
+      <c r="J28" s="9">
         <f t="shared" si="7"/>
         <v>47713.499999999927</v>
       </c>
-      <c r="I28" s="9">
+      <c r="K28" s="9">
         <f t="shared" si="1"/>
         <v>47714.199999999924</v>
       </c>
-      <c r="J28" s="25">
+      <c r="L28" s="25">
         <f t="shared" si="8"/>
         <v>47728.499999999927</v>
       </c>
-      <c r="K28" s="25">
+      <c r="M28" s="25">
         <f t="shared" si="9"/>
         <v>47729.499999999927</v>
       </c>
-      <c r="L28" s="9">
+      <c r="N28" s="9">
         <f t="shared" si="10"/>
         <v>48008</v>
       </c>
-      <c r="M28" s="9">
+      <c r="O28" s="9">
         <f t="shared" si="11"/>
         <v>48012</v>
       </c>
-      <c r="N28" s="42">
+      <c r="P28" s="42">
         <f t="shared" si="12"/>
         <v>48015</v>
       </c>
-      <c r="O28" s="42">
+      <c r="Q28" s="42">
         <f t="shared" si="13"/>
         <v>48020</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>27</v>
       </c>
@@ -7360,54 +7584,62 @@
       </c>
       <c r="D29" s="25">
         <f t="shared" si="3"/>
-        <v>47570</v>
+        <v>47625</v>
       </c>
       <c r="E29" s="25">
         <f t="shared" si="4"/>
+        <v>47626</v>
+      </c>
+      <c r="F29" s="25">
+        <f>B29-30</f>
         <v>47570</v>
       </c>
-      <c r="F29" s="25">
+      <c r="G29" s="25">
         <f t="shared" si="5"/>
+        <v>47570</v>
+      </c>
+      <c r="H29" s="25">
+        <f>B29+30</f>
         <v>47630</v>
       </c>
-      <c r="G29" s="25">
+      <c r="I29" s="25">
         <f t="shared" si="6"/>
         <v>47630</v>
       </c>
-      <c r="H29" s="9">
+      <c r="J29" s="9">
         <f t="shared" si="7"/>
         <v>47714.199999999924</v>
       </c>
-      <c r="I29" s="9">
+      <c r="K29" s="9">
         <f t="shared" si="1"/>
         <v>47714.899999999921</v>
       </c>
-      <c r="J29" s="25">
+      <c r="L29" s="25">
         <f t="shared" si="8"/>
         <v>47729.199999999924</v>
       </c>
-      <c r="K29" s="25">
+      <c r="M29" s="25">
         <f t="shared" si="9"/>
         <v>47730.199999999924</v>
       </c>
-      <c r="L29" s="9">
+      <c r="N29" s="9">
         <f t="shared" si="10"/>
         <v>48012</v>
       </c>
-      <c r="M29" s="9">
+      <c r="O29" s="9">
         <f t="shared" si="11"/>
         <v>48016</v>
       </c>
-      <c r="N29" s="42">
+      <c r="P29" s="42">
         <f t="shared" si="12"/>
         <v>48019</v>
       </c>
-      <c r="O29" s="42">
+      <c r="Q29" s="42">
         <f t="shared" si="13"/>
         <v>48024</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>28</v>
       </c>
@@ -7421,54 +7653,62 @@
       </c>
       <c r="D30" s="25">
         <f t="shared" si="3"/>
-        <v>47571</v>
+        <v>47626</v>
       </c>
       <c r="E30" s="25">
         <f t="shared" si="4"/>
+        <v>47627</v>
+      </c>
+      <c r="F30" s="25">
+        <f>B30-30</f>
         <v>47571</v>
       </c>
-      <c r="F30" s="25">
+      <c r="G30" s="25">
         <f t="shared" si="5"/>
+        <v>47571</v>
+      </c>
+      <c r="H30" s="25">
+        <f>B30+30</f>
         <v>47631</v>
       </c>
-      <c r="G30" s="25">
+      <c r="I30" s="25">
         <f t="shared" si="6"/>
         <v>47631</v>
       </c>
-      <c r="H30" s="9">
+      <c r="J30" s="9">
         <f t="shared" si="7"/>
         <v>47714.899999999921</v>
       </c>
-      <c r="I30" s="9">
+      <c r="K30" s="9">
         <f t="shared" si="1"/>
         <v>47715.599999999919</v>
       </c>
-      <c r="J30" s="25">
+      <c r="L30" s="25">
         <f t="shared" si="8"/>
         <v>47729.899999999921</v>
       </c>
-      <c r="K30" s="25">
+      <c r="M30" s="25">
         <f t="shared" si="9"/>
         <v>47730.899999999921</v>
       </c>
-      <c r="L30" s="9">
+      <c r="N30" s="9">
         <f t="shared" si="10"/>
         <v>48016</v>
       </c>
-      <c r="M30" s="9">
+      <c r="O30" s="9">
         <f t="shared" si="11"/>
         <v>48020</v>
       </c>
-      <c r="N30" s="42">
+      <c r="P30" s="42">
         <f t="shared" si="12"/>
         <v>48023</v>
       </c>
-      <c r="O30" s="42">
+      <c r="Q30" s="42">
         <f t="shared" si="13"/>
         <v>48028</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>29</v>
       </c>
@@ -7482,54 +7722,62 @@
       </c>
       <c r="D31" s="25">
         <f t="shared" si="3"/>
-        <v>47572</v>
+        <v>47627</v>
       </c>
       <c r="E31" s="25">
         <f t="shared" si="4"/>
+        <v>47628</v>
+      </c>
+      <c r="F31" s="25">
+        <f>B31-30</f>
         <v>47572</v>
       </c>
-      <c r="F31" s="25">
+      <c r="G31" s="25">
         <f t="shared" si="5"/>
+        <v>47572</v>
+      </c>
+      <c r="H31" s="25">
+        <f>B31+30</f>
         <v>47632</v>
       </c>
-      <c r="G31" s="25">
+      <c r="I31" s="25">
         <f t="shared" si="6"/>
         <v>47632</v>
       </c>
-      <c r="H31" s="9">
+      <c r="J31" s="9">
         <f t="shared" si="7"/>
         <v>47715.599999999919</v>
       </c>
-      <c r="I31" s="9">
+      <c r="K31" s="9">
         <f t="shared" si="1"/>
         <v>47716.299999999916</v>
       </c>
-      <c r="J31" s="25">
+      <c r="L31" s="25">
         <f t="shared" si="8"/>
         <v>47730.599999999919</v>
       </c>
-      <c r="K31" s="25">
+      <c r="M31" s="25">
         <f t="shared" si="9"/>
         <v>47731.599999999919</v>
       </c>
-      <c r="L31" s="9">
+      <c r="N31" s="9">
         <f t="shared" si="10"/>
         <v>48020</v>
       </c>
-      <c r="M31" s="9">
+      <c r="O31" s="9">
         <f t="shared" si="11"/>
         <v>48024</v>
       </c>
-      <c r="N31" s="42">
+      <c r="P31" s="42">
         <f t="shared" si="12"/>
         <v>48027</v>
       </c>
-      <c r="O31" s="42">
+      <c r="Q31" s="42">
         <f t="shared" si="13"/>
         <v>48032</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>30</v>
       </c>
@@ -7543,54 +7791,62 @@
       </c>
       <c r="D32" s="25">
         <f t="shared" si="3"/>
-        <v>47573</v>
+        <v>47628</v>
       </c>
       <c r="E32" s="25">
         <f t="shared" si="4"/>
+        <v>47629</v>
+      </c>
+      <c r="F32" s="25">
+        <f>B32-30</f>
         <v>47573</v>
       </c>
-      <c r="F32" s="25">
+      <c r="G32" s="25">
         <f t="shared" si="5"/>
+        <v>47573</v>
+      </c>
+      <c r="H32" s="25">
+        <f>B32+30</f>
         <v>47633</v>
       </c>
-      <c r="G32" s="25">
+      <c r="I32" s="25">
         <f t="shared" si="6"/>
         <v>47633</v>
       </c>
-      <c r="H32" s="9">
+      <c r="J32" s="9">
         <f t="shared" si="7"/>
         <v>47716.299999999916</v>
       </c>
-      <c r="I32" s="9">
+      <c r="K32" s="9">
         <f t="shared" si="1"/>
         <v>47716.999999999913</v>
       </c>
-      <c r="J32" s="25">
+      <c r="L32" s="25">
         <f t="shared" si="8"/>
         <v>47731.299999999916</v>
       </c>
-      <c r="K32" s="25">
+      <c r="M32" s="25">
         <f t="shared" si="9"/>
         <v>47732.299999999916</v>
       </c>
-      <c r="L32" s="9">
+      <c r="N32" s="9">
         <f t="shared" si="10"/>
         <v>48024</v>
       </c>
-      <c r="M32" s="9">
+      <c r="O32" s="9">
         <f t="shared" si="11"/>
         <v>48028</v>
       </c>
-      <c r="N32" s="42">
+      <c r="P32" s="42">
         <f t="shared" si="12"/>
         <v>48031</v>
       </c>
-      <c r="O32" s="42">
+      <c r="Q32" s="42">
         <f t="shared" si="13"/>
         <v>48036</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>31</v>
       </c>
@@ -7604,54 +7860,62 @@
       </c>
       <c r="D33" s="25">
         <f t="shared" si="3"/>
-        <v>47574</v>
+        <v>47629</v>
       </c>
       <c r="E33" s="25">
         <f t="shared" si="4"/>
+        <v>47630</v>
+      </c>
+      <c r="F33" s="25">
+        <f>B33-30</f>
         <v>47574</v>
       </c>
-      <c r="F33" s="25">
+      <c r="G33" s="25">
         <f t="shared" si="5"/>
+        <v>47574</v>
+      </c>
+      <c r="H33" s="25">
+        <f>B33+30</f>
         <v>47634</v>
       </c>
-      <c r="G33" s="25">
+      <c r="I33" s="25">
         <f t="shared" si="6"/>
         <v>47634</v>
       </c>
-      <c r="H33" s="9">
+      <c r="J33" s="9">
         <f t="shared" si="7"/>
         <v>47716.999999999913</v>
       </c>
-      <c r="I33" s="9">
+      <c r="K33" s="9">
         <f t="shared" si="1"/>
         <v>47717.69999999991</v>
       </c>
-      <c r="J33" s="25">
+      <c r="L33" s="25">
         <f t="shared" si="8"/>
         <v>47731.999999999913</v>
       </c>
-      <c r="K33" s="25">
+      <c r="M33" s="25">
         <f t="shared" si="9"/>
         <v>47732.999999999913</v>
       </c>
-      <c r="L33" s="9">
+      <c r="N33" s="9">
         <f t="shared" si="10"/>
         <v>48028</v>
       </c>
-      <c r="M33" s="9">
+      <c r="O33" s="9">
         <f t="shared" si="11"/>
         <v>48032</v>
       </c>
-      <c r="N33" s="42">
+      <c r="P33" s="42">
         <f t="shared" si="12"/>
         <v>48035</v>
       </c>
-      <c r="O33" s="42">
+      <c r="Q33" s="42">
         <f t="shared" si="13"/>
         <v>48040</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>32</v>
       </c>
@@ -7665,54 +7929,62 @@
       </c>
       <c r="D34" s="25">
         <f t="shared" si="3"/>
-        <v>47575</v>
+        <v>47630</v>
       </c>
       <c r="E34" s="25">
         <f t="shared" si="4"/>
+        <v>47631</v>
+      </c>
+      <c r="F34" s="25">
+        <f>B34-30</f>
         <v>47575</v>
       </c>
-      <c r="F34" s="25">
+      <c r="G34" s="25">
         <f t="shared" si="5"/>
+        <v>47575</v>
+      </c>
+      <c r="H34" s="25">
+        <f>B34+30</f>
         <v>47635</v>
       </c>
-      <c r="G34" s="25">
+      <c r="I34" s="25">
         <f t="shared" si="6"/>
         <v>47635</v>
       </c>
-      <c r="H34" s="9">
+      <c r="J34" s="9">
         <f t="shared" si="7"/>
         <v>47717.69999999991</v>
       </c>
-      <c r="I34" s="9">
+      <c r="K34" s="9">
         <f t="shared" si="1"/>
         <v>47718.399999999907</v>
       </c>
-      <c r="J34" s="25">
+      <c r="L34" s="25">
         <f t="shared" si="8"/>
         <v>47732.69999999991</v>
       </c>
-      <c r="K34" s="25">
+      <c r="M34" s="25">
         <f t="shared" si="9"/>
         <v>47733.69999999991</v>
       </c>
-      <c r="L34" s="9">
+      <c r="N34" s="9">
         <f t="shared" si="10"/>
         <v>48032</v>
       </c>
-      <c r="M34" s="9">
+      <c r="O34" s="9">
         <f t="shared" si="11"/>
         <v>48036</v>
       </c>
-      <c r="N34" s="42">
+      <c r="P34" s="42">
         <f t="shared" si="12"/>
         <v>48039</v>
       </c>
-      <c r="O34" s="42">
+      <c r="Q34" s="42">
         <f t="shared" si="13"/>
         <v>48044</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>33</v>
       </c>
@@ -7726,54 +7998,62 @@
       </c>
       <c r="D35" s="25">
         <f t="shared" si="3"/>
-        <v>47576</v>
+        <v>47631</v>
       </c>
       <c r="E35" s="25">
         <f t="shared" si="4"/>
+        <v>47632</v>
+      </c>
+      <c r="F35" s="25">
+        <f>B35-30</f>
         <v>47576</v>
       </c>
-      <c r="F35" s="25">
+      <c r="G35" s="25">
         <f t="shared" si="5"/>
+        <v>47576</v>
+      </c>
+      <c r="H35" s="25">
+        <f>B35+30</f>
         <v>47636</v>
       </c>
-      <c r="G35" s="25">
+      <c r="I35" s="25">
         <f t="shared" si="6"/>
         <v>47636</v>
       </c>
-      <c r="H35" s="9">
+      <c r="J35" s="9">
         <f t="shared" si="7"/>
         <v>47718.399999999907</v>
       </c>
-      <c r="I35" s="9">
-        <f t="shared" ref="I35:I57" si="15">H35+0.7</f>
+      <c r="K35" s="9">
+        <f t="shared" ref="K35:K57" si="15">J35+0.7</f>
         <v>47719.099999999904</v>
       </c>
-      <c r="J35" s="25">
+      <c r="L35" s="25">
         <f t="shared" si="8"/>
         <v>47733.399999999907</v>
       </c>
-      <c r="K35" s="25">
+      <c r="M35" s="25">
         <f t="shared" si="9"/>
         <v>47734.399999999907</v>
       </c>
-      <c r="L35" s="9">
+      <c r="N35" s="9">
         <f t="shared" si="10"/>
         <v>48036</v>
       </c>
-      <c r="M35" s="9">
+      <c r="O35" s="9">
         <f t="shared" si="11"/>
         <v>48040</v>
       </c>
-      <c r="N35" s="42">
+      <c r="P35" s="42">
         <f t="shared" si="12"/>
         <v>48043</v>
       </c>
-      <c r="O35" s="42">
+      <c r="Q35" s="42">
         <f t="shared" si="13"/>
         <v>48048</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>34</v>
       </c>
@@ -7787,54 +8067,62 @@
       </c>
       <c r="D36" s="25">
         <f t="shared" si="3"/>
-        <v>47577</v>
+        <v>47632</v>
       </c>
       <c r="E36" s="25">
         <f t="shared" si="4"/>
+        <v>47633</v>
+      </c>
+      <c r="F36" s="25">
+        <f>B36-30</f>
         <v>47577</v>
       </c>
-      <c r="F36" s="25">
+      <c r="G36" s="25">
         <f t="shared" si="5"/>
+        <v>47577</v>
+      </c>
+      <c r="H36" s="25">
+        <f>B36+30</f>
         <v>47637</v>
       </c>
-      <c r="G36" s="25">
+      <c r="I36" s="25">
         <f t="shared" si="6"/>
         <v>47637</v>
       </c>
-      <c r="H36" s="9">
-        <f t="shared" ref="H36:H57" si="17">H35+0.7</f>
+      <c r="J36" s="9">
+        <f t="shared" ref="J36:J57" si="17">J35+0.7</f>
         <v>47719.099999999904</v>
       </c>
-      <c r="I36" s="9">
+      <c r="K36" s="9">
         <f t="shared" si="15"/>
         <v>47719.799999999901</v>
       </c>
-      <c r="J36" s="25">
+      <c r="L36" s="25">
         <f t="shared" si="8"/>
         <v>47734.099999999904</v>
       </c>
-      <c r="K36" s="25">
+      <c r="M36" s="25">
         <f t="shared" si="9"/>
         <v>47735.099999999904</v>
       </c>
-      <c r="L36" s="9">
-        <f t="shared" ref="L36:L52" si="18">L35+4</f>
+      <c r="N36" s="9">
+        <f t="shared" ref="N36:N52" si="18">N35+4</f>
         <v>48040</v>
       </c>
-      <c r="M36" s="9">
-        <f t="shared" ref="M36:M52" si="19">M35+4</f>
+      <c r="O36" s="9">
+        <f t="shared" ref="O36:O52" si="19">O35+4</f>
         <v>48044</v>
       </c>
-      <c r="N36" s="42">
+      <c r="P36" s="42">
         <f t="shared" si="12"/>
         <v>48047</v>
       </c>
-      <c r="O36" s="42">
+      <c r="Q36" s="42">
         <f t="shared" si="13"/>
         <v>48052</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>35</v>
       </c>
@@ -7848,54 +8136,62 @@
       </c>
       <c r="D37" s="25">
         <f t="shared" si="3"/>
-        <v>47578</v>
+        <v>47633</v>
       </c>
       <c r="E37" s="25">
         <f t="shared" si="4"/>
+        <v>47634</v>
+      </c>
+      <c r="F37" s="25">
+        <f>B37-30</f>
         <v>47578</v>
       </c>
-      <c r="F37" s="25">
+      <c r="G37" s="25">
         <f t="shared" si="5"/>
+        <v>47578</v>
+      </c>
+      <c r="H37" s="25">
+        <f>B37+30</f>
         <v>47638</v>
       </c>
-      <c r="G37" s="25">
+      <c r="I37" s="25">
         <f t="shared" si="6"/>
         <v>47638</v>
       </c>
-      <c r="H37" s="9">
+      <c r="J37" s="9">
         <f t="shared" si="17"/>
         <v>47719.799999999901</v>
       </c>
-      <c r="I37" s="9">
+      <c r="K37" s="9">
         <f t="shared" si="15"/>
         <v>47720.499999999898</v>
       </c>
-      <c r="J37" s="25">
+      <c r="L37" s="25">
         <f t="shared" si="8"/>
         <v>47734.799999999901</v>
       </c>
-      <c r="K37" s="25">
+      <c r="M37" s="25">
         <f t="shared" si="9"/>
         <v>47735.799999999901</v>
       </c>
-      <c r="L37" s="9">
+      <c r="N37" s="9">
         <f t="shared" si="18"/>
         <v>48044</v>
       </c>
-      <c r="M37" s="9">
+      <c r="O37" s="9">
         <f t="shared" si="19"/>
         <v>48048</v>
       </c>
-      <c r="N37" s="42">
+      <c r="P37" s="42">
         <f t="shared" si="12"/>
         <v>48051</v>
       </c>
-      <c r="O37" s="42">
+      <c r="Q37" s="42">
         <f t="shared" si="13"/>
         <v>48056</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>36</v>
       </c>
@@ -7909,54 +8205,62 @@
       </c>
       <c r="D38" s="25">
         <f t="shared" si="3"/>
-        <v>47579</v>
+        <v>47634</v>
       </c>
       <c r="E38" s="25">
         <f t="shared" si="4"/>
+        <v>47635</v>
+      </c>
+      <c r="F38" s="25">
+        <f>B38-30</f>
         <v>47579</v>
       </c>
-      <c r="F38" s="25">
+      <c r="G38" s="25">
         <f t="shared" si="5"/>
+        <v>47579</v>
+      </c>
+      <c r="H38" s="25">
+        <f>B38+30</f>
         <v>47639</v>
       </c>
-      <c r="G38" s="25">
+      <c r="I38" s="25">
         <f t="shared" si="6"/>
         <v>47639</v>
       </c>
-      <c r="H38" s="9">
+      <c r="J38" s="9">
         <f t="shared" si="17"/>
         <v>47720.499999999898</v>
       </c>
-      <c r="I38" s="9">
+      <c r="K38" s="9">
         <f t="shared" si="15"/>
         <v>47721.199999999895</v>
       </c>
-      <c r="J38" s="25">
+      <c r="L38" s="25">
         <f t="shared" si="8"/>
         <v>47735.499999999898</v>
       </c>
-      <c r="K38" s="25">
+      <c r="M38" s="25">
         <f t="shared" si="9"/>
         <v>47736.499999999898</v>
       </c>
-      <c r="L38" s="9">
+      <c r="N38" s="9">
         <f t="shared" si="18"/>
         <v>48048</v>
       </c>
-      <c r="M38" s="9">
+      <c r="O38" s="9">
         <f t="shared" si="19"/>
         <v>48052</v>
       </c>
-      <c r="N38" s="42">
+      <c r="P38" s="42">
         <f t="shared" si="12"/>
         <v>48055</v>
       </c>
-      <c r="O38" s="42">
+      <c r="Q38" s="42">
         <f t="shared" si="13"/>
         <v>48060</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>37</v>
       </c>
@@ -7970,54 +8274,62 @@
       </c>
       <c r="D39" s="25">
         <f t="shared" si="3"/>
-        <v>47580</v>
+        <v>47635</v>
       </c>
       <c r="E39" s="25">
         <f t="shared" si="4"/>
+        <v>47636</v>
+      </c>
+      <c r="F39" s="25">
+        <f>B39-30</f>
         <v>47580</v>
       </c>
-      <c r="F39" s="25">
+      <c r="G39" s="25">
         <f t="shared" si="5"/>
+        <v>47580</v>
+      </c>
+      <c r="H39" s="25">
+        <f>B39+30</f>
         <v>47640</v>
       </c>
-      <c r="G39" s="25">
+      <c r="I39" s="25">
         <f t="shared" si="6"/>
         <v>47640</v>
       </c>
-      <c r="H39" s="9">
+      <c r="J39" s="9">
         <f t="shared" si="17"/>
         <v>47721.199999999895</v>
       </c>
-      <c r="I39" s="9">
+      <c r="K39" s="9">
         <f t="shared" si="15"/>
         <v>47721.899999999892</v>
       </c>
-      <c r="J39" s="25">
+      <c r="L39" s="25">
         <f t="shared" si="8"/>
         <v>47736.199999999895</v>
       </c>
-      <c r="K39" s="25">
+      <c r="M39" s="25">
         <f t="shared" si="9"/>
         <v>47737.199999999895</v>
       </c>
-      <c r="L39" s="9">
+      <c r="N39" s="9">
         <f t="shared" si="18"/>
         <v>48052</v>
       </c>
-      <c r="M39" s="9">
+      <c r="O39" s="9">
         <f t="shared" si="19"/>
         <v>48056</v>
       </c>
-      <c r="N39" s="42">
+      <c r="P39" s="42">
         <f t="shared" si="12"/>
         <v>48059</v>
       </c>
-      <c r="O39" s="42">
+      <c r="Q39" s="42">
         <f t="shared" si="13"/>
         <v>48064</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>38</v>
       </c>
@@ -8031,54 +8343,62 @@
       </c>
       <c r="D40" s="25">
         <f t="shared" si="3"/>
-        <v>47581</v>
+        <v>47636</v>
       </c>
       <c r="E40" s="25">
         <f t="shared" si="4"/>
+        <v>47637</v>
+      </c>
+      <c r="F40" s="25">
+        <f>B40-30</f>
         <v>47581</v>
       </c>
-      <c r="F40" s="25">
+      <c r="G40" s="25">
         <f t="shared" si="5"/>
+        <v>47581</v>
+      </c>
+      <c r="H40" s="25">
+        <f>B40+30</f>
         <v>47641</v>
       </c>
-      <c r="G40" s="25">
+      <c r="I40" s="25">
         <f t="shared" si="6"/>
         <v>47641</v>
       </c>
-      <c r="H40" s="9">
+      <c r="J40" s="9">
         <f t="shared" si="17"/>
         <v>47721.899999999892</v>
       </c>
-      <c r="I40" s="9">
+      <c r="K40" s="9">
         <f t="shared" si="15"/>
         <v>47722.599999999889</v>
       </c>
-      <c r="J40" s="25">
+      <c r="L40" s="25">
         <f t="shared" si="8"/>
         <v>47736.899999999892</v>
       </c>
-      <c r="K40" s="25">
+      <c r="M40" s="25">
         <f t="shared" si="9"/>
         <v>47737.899999999892</v>
       </c>
-      <c r="L40" s="9">
+      <c r="N40" s="9">
         <f t="shared" si="18"/>
         <v>48056</v>
       </c>
-      <c r="M40" s="9">
+      <c r="O40" s="9">
         <f t="shared" si="19"/>
         <v>48060</v>
       </c>
-      <c r="N40" s="42">
+      <c r="P40" s="42">
         <f t="shared" si="12"/>
         <v>48063</v>
       </c>
-      <c r="O40" s="42">
+      <c r="Q40" s="42">
         <f t="shared" si="13"/>
         <v>48068</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>39</v>
       </c>
@@ -8092,54 +8412,62 @@
       </c>
       <c r="D41" s="25">
         <f t="shared" si="3"/>
-        <v>47582</v>
+        <v>47637</v>
       </c>
       <c r="E41" s="25">
         <f t="shared" si="4"/>
+        <v>47638</v>
+      </c>
+      <c r="F41" s="25">
+        <f>B41-30</f>
         <v>47582</v>
       </c>
-      <c r="F41" s="25">
+      <c r="G41" s="25">
         <f t="shared" si="5"/>
+        <v>47582</v>
+      </c>
+      <c r="H41" s="25">
+        <f>B41+30</f>
         <v>47642</v>
       </c>
-      <c r="G41" s="25">
+      <c r="I41" s="25">
         <f t="shared" si="6"/>
         <v>47642</v>
       </c>
-      <c r="H41" s="9">
+      <c r="J41" s="9">
         <f t="shared" si="17"/>
         <v>47722.599999999889</v>
       </c>
-      <c r="I41" s="9">
+      <c r="K41" s="9">
         <f t="shared" si="15"/>
         <v>47723.299999999886</v>
       </c>
-      <c r="J41" s="25">
+      <c r="L41" s="25">
         <f t="shared" si="8"/>
         <v>47737.599999999889</v>
       </c>
-      <c r="K41" s="25">
+      <c r="M41" s="25">
         <f t="shared" si="9"/>
         <v>47738.599999999889</v>
       </c>
-      <c r="L41" s="9">
+      <c r="N41" s="9">
         <f t="shared" si="18"/>
         <v>48060</v>
       </c>
-      <c r="M41" s="9">
+      <c r="O41" s="9">
         <f t="shared" si="19"/>
         <v>48064</v>
       </c>
-      <c r="N41" s="42">
+      <c r="P41" s="42">
         <f t="shared" si="12"/>
         <v>48067</v>
       </c>
-      <c r="O41" s="42">
+      <c r="Q41" s="42">
         <f t="shared" si="13"/>
         <v>48072</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>40</v>
       </c>
@@ -8153,54 +8481,62 @@
       </c>
       <c r="D42" s="25">
         <f t="shared" si="3"/>
-        <v>47583</v>
+        <v>47638</v>
       </c>
       <c r="E42" s="25">
         <f t="shared" si="4"/>
+        <v>47639</v>
+      </c>
+      <c r="F42" s="25">
+        <f>B42-30</f>
         <v>47583</v>
       </c>
-      <c r="F42" s="25">
+      <c r="G42" s="25">
         <f t="shared" si="5"/>
+        <v>47583</v>
+      </c>
+      <c r="H42" s="25">
+        <f>B42+30</f>
         <v>47643</v>
       </c>
-      <c r="G42" s="25">
+      <c r="I42" s="25">
         <f t="shared" si="6"/>
         <v>47643</v>
       </c>
-      <c r="H42" s="9">
+      <c r="J42" s="9">
         <f t="shared" si="17"/>
         <v>47723.299999999886</v>
       </c>
-      <c r="I42" s="9">
+      <c r="K42" s="9">
         <f t="shared" si="15"/>
         <v>47723.999999999884</v>
       </c>
-      <c r="J42" s="25">
+      <c r="L42" s="25">
         <f t="shared" si="8"/>
         <v>47738.299999999886</v>
       </c>
-      <c r="K42" s="25">
+      <c r="M42" s="25">
         <f t="shared" si="9"/>
         <v>47739.299999999886</v>
       </c>
-      <c r="L42" s="9">
+      <c r="N42" s="9">
         <f t="shared" si="18"/>
         <v>48064</v>
       </c>
-      <c r="M42" s="9">
+      <c r="O42" s="9">
         <f t="shared" si="19"/>
         <v>48068</v>
       </c>
-      <c r="N42" s="42">
+      <c r="P42" s="42">
         <f t="shared" si="12"/>
         <v>48071</v>
       </c>
-      <c r="O42" s="42">
+      <c r="Q42" s="42">
         <f t="shared" si="13"/>
         <v>48076</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>41</v>
       </c>
@@ -8214,54 +8550,62 @@
       </c>
       <c r="D43" s="25">
         <f t="shared" si="3"/>
-        <v>47584</v>
+        <v>47639</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="4"/>
+        <v>47640</v>
+      </c>
+      <c r="F43" s="25">
+        <f>B43-30</f>
         <v>47584</v>
       </c>
-      <c r="F43" s="25">
+      <c r="G43" s="25">
         <f t="shared" si="5"/>
+        <v>47584</v>
+      </c>
+      <c r="H43" s="25">
+        <f>B43+30</f>
         <v>47644</v>
       </c>
-      <c r="G43" s="25">
+      <c r="I43" s="25">
         <f t="shared" si="6"/>
         <v>47644</v>
       </c>
-      <c r="H43" s="9">
+      <c r="J43" s="9">
         <f t="shared" si="17"/>
         <v>47723.999999999884</v>
       </c>
-      <c r="I43" s="9">
+      <c r="K43" s="9">
         <f t="shared" si="15"/>
         <v>47724.699999999881</v>
       </c>
-      <c r="J43" s="25">
+      <c r="L43" s="25">
         <f t="shared" si="8"/>
         <v>47738.999999999884</v>
       </c>
-      <c r="K43" s="25">
+      <c r="M43" s="25">
         <f t="shared" si="9"/>
         <v>47739.999999999884</v>
       </c>
-      <c r="L43" s="9">
+      <c r="N43" s="9">
         <f t="shared" si="18"/>
         <v>48068</v>
       </c>
-      <c r="M43" s="9">
+      <c r="O43" s="9">
         <f t="shared" si="19"/>
         <v>48072</v>
       </c>
-      <c r="N43" s="42">
+      <c r="P43" s="42">
         <f t="shared" si="12"/>
         <v>48075</v>
       </c>
-      <c r="O43" s="42">
+      <c r="Q43" s="42">
         <f t="shared" si="13"/>
         <v>48080</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>42</v>
       </c>
@@ -8275,54 +8619,62 @@
       </c>
       <c r="D44" s="25">
         <f t="shared" si="3"/>
-        <v>47585</v>
+        <v>47640</v>
       </c>
       <c r="E44" s="25">
         <f t="shared" si="4"/>
+        <v>47641</v>
+      </c>
+      <c r="F44" s="25">
+        <f>B44-30</f>
         <v>47585</v>
       </c>
-      <c r="F44" s="25">
+      <c r="G44" s="25">
         <f t="shared" si="5"/>
+        <v>47585</v>
+      </c>
+      <c r="H44" s="25">
+        <f>B44+30</f>
         <v>47645</v>
       </c>
-      <c r="G44" s="25">
+      <c r="I44" s="25">
         <f t="shared" si="6"/>
         <v>47645</v>
       </c>
-      <c r="H44" s="9">
+      <c r="J44" s="9">
         <f t="shared" si="17"/>
         <v>47724.699999999881</v>
       </c>
-      <c r="I44" s="9">
+      <c r="K44" s="9">
         <f t="shared" si="15"/>
         <v>47725.399999999878</v>
       </c>
-      <c r="J44" s="25">
+      <c r="L44" s="25">
         <f t="shared" si="8"/>
         <v>47739.699999999881</v>
       </c>
-      <c r="K44" s="25">
+      <c r="M44" s="25">
         <f t="shared" si="9"/>
         <v>47740.699999999881</v>
       </c>
-      <c r="L44" s="9">
+      <c r="N44" s="9">
         <f t="shared" si="18"/>
         <v>48072</v>
       </c>
-      <c r="M44" s="9">
+      <c r="O44" s="9">
         <f t="shared" si="19"/>
         <v>48076</v>
       </c>
-      <c r="N44" s="42">
+      <c r="P44" s="42">
         <f t="shared" si="12"/>
         <v>48079</v>
       </c>
-      <c r="O44" s="42">
+      <c r="Q44" s="42">
         <f t="shared" si="13"/>
         <v>48084</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>43</v>
       </c>
@@ -8336,54 +8688,62 @@
       </c>
       <c r="D45" s="25">
         <f t="shared" si="3"/>
-        <v>47586</v>
+        <v>47641</v>
       </c>
       <c r="E45" s="25">
         <f t="shared" si="4"/>
+        <v>47642</v>
+      </c>
+      <c r="F45" s="25">
+        <f>B45-30</f>
         <v>47586</v>
       </c>
-      <c r="F45" s="25">
+      <c r="G45" s="25">
         <f t="shared" si="5"/>
+        <v>47586</v>
+      </c>
+      <c r="H45" s="25">
+        <f>B45+30</f>
         <v>47646</v>
       </c>
-      <c r="G45" s="25">
+      <c r="I45" s="25">
         <f t="shared" si="6"/>
         <v>47646</v>
       </c>
-      <c r="H45" s="9">
+      <c r="J45" s="9">
         <f t="shared" si="17"/>
         <v>47725.399999999878</v>
       </c>
-      <c r="I45" s="9">
+      <c r="K45" s="9">
         <f t="shared" si="15"/>
         <v>47726.099999999875</v>
       </c>
-      <c r="J45" s="25">
+      <c r="L45" s="25">
         <f t="shared" si="8"/>
         <v>47740.399999999878</v>
       </c>
-      <c r="K45" s="25">
+      <c r="M45" s="25">
         <f t="shared" si="9"/>
         <v>47741.399999999878</v>
       </c>
-      <c r="L45" s="9">
+      <c r="N45" s="9">
         <f t="shared" si="18"/>
         <v>48076</v>
       </c>
-      <c r="M45" s="9">
+      <c r="O45" s="9">
         <f t="shared" si="19"/>
         <v>48080</v>
       </c>
-      <c r="N45" s="42">
+      <c r="P45" s="42">
         <f t="shared" si="12"/>
         <v>48083</v>
       </c>
-      <c r="O45" s="42">
+      <c r="Q45" s="42">
         <f t="shared" si="13"/>
         <v>48088</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>44</v>
       </c>
@@ -8397,54 +8757,62 @@
       </c>
       <c r="D46" s="25">
         <f t="shared" si="3"/>
-        <v>47587</v>
+        <v>47642</v>
       </c>
       <c r="E46" s="25">
         <f t="shared" si="4"/>
+        <v>47643</v>
+      </c>
+      <c r="F46" s="25">
+        <f>B46-30</f>
         <v>47587</v>
       </c>
-      <c r="F46" s="25">
+      <c r="G46" s="25">
         <f t="shared" si="5"/>
+        <v>47587</v>
+      </c>
+      <c r="H46" s="25">
+        <f>B46+30</f>
         <v>47647</v>
       </c>
-      <c r="G46" s="25">
+      <c r="I46" s="25">
         <f t="shared" si="6"/>
         <v>47647</v>
       </c>
-      <c r="H46" s="9">
+      <c r="J46" s="9">
         <f t="shared" si="17"/>
         <v>47726.099999999875</v>
       </c>
-      <c r="I46" s="9">
+      <c r="K46" s="9">
         <f t="shared" si="15"/>
         <v>47726.799999999872</v>
       </c>
-      <c r="J46" s="25">
+      <c r="L46" s="25">
         <f t="shared" si="8"/>
         <v>47741.099999999875</v>
       </c>
-      <c r="K46" s="25">
+      <c r="M46" s="25">
         <f t="shared" si="9"/>
         <v>47742.099999999875</v>
       </c>
-      <c r="L46" s="9">
+      <c r="N46" s="9">
         <f t="shared" si="18"/>
         <v>48080</v>
       </c>
-      <c r="M46" s="9">
+      <c r="O46" s="9">
         <f t="shared" si="19"/>
         <v>48084</v>
       </c>
-      <c r="N46" s="42">
+      <c r="P46" s="42">
         <f t="shared" si="12"/>
         <v>48087</v>
       </c>
-      <c r="O46" s="42">
+      <c r="Q46" s="42">
         <f t="shared" si="13"/>
         <v>48092</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>45</v>
       </c>
@@ -8458,54 +8826,62 @@
       </c>
       <c r="D47" s="25">
         <f t="shared" si="3"/>
-        <v>47588</v>
+        <v>47643</v>
       </c>
       <c r="E47" s="25">
         <f t="shared" si="4"/>
+        <v>47644</v>
+      </c>
+      <c r="F47" s="25">
+        <f>B47-30</f>
         <v>47588</v>
       </c>
-      <c r="F47" s="25">
+      <c r="G47" s="25">
         <f t="shared" si="5"/>
+        <v>47588</v>
+      </c>
+      <c r="H47" s="25">
+        <f>B47+30</f>
         <v>47648</v>
       </c>
-      <c r="G47" s="25">
+      <c r="I47" s="25">
         <f t="shared" si="6"/>
         <v>47648</v>
       </c>
-      <c r="H47" s="9">
+      <c r="J47" s="9">
         <f t="shared" si="17"/>
         <v>47726.799999999872</v>
       </c>
-      <c r="I47" s="9">
+      <c r="K47" s="9">
         <f t="shared" si="15"/>
         <v>47727.499999999869</v>
       </c>
-      <c r="J47" s="25">
+      <c r="L47" s="25">
         <f t="shared" si="8"/>
         <v>47741.799999999872</v>
       </c>
-      <c r="K47" s="25">
+      <c r="M47" s="25">
         <f t="shared" si="9"/>
         <v>47742.799999999872</v>
       </c>
-      <c r="L47" s="9">
+      <c r="N47" s="9">
         <f t="shared" si="18"/>
         <v>48084</v>
       </c>
-      <c r="M47" s="9">
+      <c r="O47" s="9">
         <f t="shared" si="19"/>
         <v>48088</v>
       </c>
-      <c r="N47" s="42">
+      <c r="P47" s="42">
         <f t="shared" si="12"/>
         <v>48091</v>
       </c>
-      <c r="O47" s="42">
+      <c r="Q47" s="42">
         <f t="shared" si="13"/>
         <v>48096</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>46</v>
       </c>
@@ -8519,54 +8895,62 @@
       </c>
       <c r="D48" s="25">
         <f t="shared" si="3"/>
-        <v>47589</v>
+        <v>47644</v>
       </c>
       <c r="E48" s="25">
         <f t="shared" si="4"/>
+        <v>47645</v>
+      </c>
+      <c r="F48" s="25">
+        <f>B48-30</f>
         <v>47589</v>
       </c>
-      <c r="F48" s="25">
+      <c r="G48" s="25">
         <f t="shared" si="5"/>
+        <v>47589</v>
+      </c>
+      <c r="H48" s="25">
+        <f>B48+30</f>
         <v>47649</v>
       </c>
-      <c r="G48" s="25">
+      <c r="I48" s="25">
         <f t="shared" si="6"/>
         <v>47649</v>
       </c>
-      <c r="H48" s="9">
+      <c r="J48" s="9">
         <f t="shared" si="17"/>
         <v>47727.499999999869</v>
       </c>
-      <c r="I48" s="9">
+      <c r="K48" s="9">
         <f t="shared" si="15"/>
         <v>47728.199999999866</v>
       </c>
-      <c r="J48" s="25">
+      <c r="L48" s="25">
         <f t="shared" si="8"/>
         <v>47742.499999999869</v>
       </c>
-      <c r="K48" s="25">
+      <c r="M48" s="25">
         <f t="shared" si="9"/>
         <v>47743.499999999869</v>
       </c>
-      <c r="L48" s="9">
+      <c r="N48" s="9">
         <f t="shared" si="18"/>
         <v>48088</v>
       </c>
-      <c r="M48" s="9">
+      <c r="O48" s="9">
         <f t="shared" si="19"/>
         <v>48092</v>
       </c>
-      <c r="N48" s="42">
+      <c r="P48" s="42">
         <f t="shared" si="12"/>
         <v>48095</v>
       </c>
-      <c r="O48" s="42">
+      <c r="Q48" s="42">
         <f t="shared" si="13"/>
         <v>48100</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>47</v>
       </c>
@@ -8580,54 +8964,62 @@
       </c>
       <c r="D49" s="25">
         <f t="shared" si="3"/>
-        <v>47590</v>
+        <v>47645</v>
       </c>
       <c r="E49" s="25">
         <f t="shared" si="4"/>
+        <v>47646</v>
+      </c>
+      <c r="F49" s="25">
+        <f>B49-30</f>
         <v>47590</v>
       </c>
-      <c r="F49" s="25">
+      <c r="G49" s="25">
         <f t="shared" si="5"/>
+        <v>47590</v>
+      </c>
+      <c r="H49" s="25">
+        <f>B49+30</f>
         <v>47650</v>
       </c>
-      <c r="G49" s="25">
+      <c r="I49" s="25">
         <f t="shared" si="6"/>
         <v>47650</v>
       </c>
-      <c r="H49" s="9">
+      <c r="J49" s="9">
         <f t="shared" si="17"/>
         <v>47728.199999999866</v>
       </c>
-      <c r="I49" s="9">
+      <c r="K49" s="9">
         <f t="shared" si="15"/>
         <v>47728.899999999863</v>
       </c>
-      <c r="J49" s="25">
+      <c r="L49" s="25">
         <f t="shared" si="8"/>
         <v>47743.199999999866</v>
       </c>
-      <c r="K49" s="25">
+      <c r="M49" s="25">
         <f t="shared" si="9"/>
         <v>47744.199999999866</v>
       </c>
-      <c r="L49" s="9">
+      <c r="N49" s="9">
         <f t="shared" si="18"/>
         <v>48092</v>
       </c>
-      <c r="M49" s="9">
+      <c r="O49" s="9">
         <f t="shared" si="19"/>
         <v>48096</v>
       </c>
-      <c r="N49" s="42">
+      <c r="P49" s="42">
         <f t="shared" si="12"/>
         <v>48099</v>
       </c>
-      <c r="O49" s="42">
+      <c r="Q49" s="42">
         <f t="shared" si="13"/>
         <v>48104</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>48</v>
       </c>
@@ -8641,54 +9033,62 @@
       </c>
       <c r="D50" s="25">
         <f t="shared" si="3"/>
-        <v>47591</v>
+        <v>47646</v>
       </c>
       <c r="E50" s="25">
         <f t="shared" si="4"/>
+        <v>47647</v>
+      </c>
+      <c r="F50" s="25">
+        <f>B50-30</f>
         <v>47591</v>
       </c>
-      <c r="F50" s="25">
+      <c r="G50" s="25">
         <f t="shared" si="5"/>
+        <v>47591</v>
+      </c>
+      <c r="H50" s="25">
+        <f>B50+30</f>
         <v>47651</v>
       </c>
-      <c r="G50" s="25">
+      <c r="I50" s="25">
         <f t="shared" si="6"/>
         <v>47651</v>
       </c>
-      <c r="H50" s="9">
+      <c r="J50" s="9">
         <f t="shared" si="17"/>
         <v>47728.899999999863</v>
       </c>
-      <c r="I50" s="9">
+      <c r="K50" s="9">
         <f t="shared" si="15"/>
         <v>47729.59999999986</v>
       </c>
-      <c r="J50" s="25">
+      <c r="L50" s="25">
         <f t="shared" si="8"/>
         <v>47743.899999999863</v>
       </c>
-      <c r="K50" s="25">
+      <c r="M50" s="25">
         <f t="shared" si="9"/>
         <v>47744.899999999863</v>
       </c>
-      <c r="L50" s="9">
+      <c r="N50" s="9">
         <f t="shared" si="18"/>
         <v>48096</v>
       </c>
-      <c r="M50" s="9">
+      <c r="O50" s="9">
         <f t="shared" si="19"/>
         <v>48100</v>
       </c>
-      <c r="N50" s="42">
+      <c r="P50" s="42">
         <f t="shared" si="12"/>
         <v>48103</v>
       </c>
-      <c r="O50" s="42">
+      <c r="Q50" s="42">
         <f t="shared" si="13"/>
         <v>48108</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>49</v>
       </c>
@@ -8702,54 +9102,62 @@
       </c>
       <c r="D51" s="25">
         <f t="shared" si="3"/>
-        <v>47592</v>
+        <v>47647</v>
       </c>
       <c r="E51" s="25">
         <f t="shared" si="4"/>
+        <v>47648</v>
+      </c>
+      <c r="F51" s="25">
+        <f>B51-30</f>
         <v>47592</v>
       </c>
-      <c r="F51" s="25">
+      <c r="G51" s="25">
         <f t="shared" si="5"/>
+        <v>47592</v>
+      </c>
+      <c r="H51" s="25">
+        <f>B51+30</f>
         <v>47652</v>
       </c>
-      <c r="G51" s="25">
+      <c r="I51" s="25">
         <f t="shared" si="6"/>
         <v>47652</v>
       </c>
-      <c r="H51" s="9">
+      <c r="J51" s="9">
         <f t="shared" si="17"/>
         <v>47729.59999999986</v>
       </c>
-      <c r="I51" s="9">
+      <c r="K51" s="9">
         <f t="shared" si="15"/>
         <v>47730.299999999857</v>
       </c>
-      <c r="J51" s="25">
+      <c r="L51" s="25">
         <f t="shared" si="8"/>
         <v>47744.59999999986</v>
       </c>
-      <c r="K51" s="25">
+      <c r="M51" s="25">
         <f t="shared" si="9"/>
         <v>47745.59999999986</v>
       </c>
-      <c r="L51" s="9">
+      <c r="N51" s="9">
         <f t="shared" si="18"/>
         <v>48100</v>
       </c>
-      <c r="M51" s="9">
+      <c r="O51" s="9">
         <f t="shared" si="19"/>
         <v>48104</v>
       </c>
-      <c r="N51" s="42">
+      <c r="P51" s="42">
         <f t="shared" si="12"/>
         <v>48107</v>
       </c>
-      <c r="O51" s="42">
+      <c r="Q51" s="42">
         <f t="shared" si="13"/>
         <v>48112</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>50</v>
       </c>
@@ -8763,54 +9171,62 @@
       </c>
       <c r="D52" s="25">
         <f t="shared" si="3"/>
-        <v>47593</v>
+        <v>47648</v>
       </c>
       <c r="E52" s="25">
         <f t="shared" si="4"/>
+        <v>47649</v>
+      </c>
+      <c r="F52" s="25">
+        <f>B52-30</f>
         <v>47593</v>
       </c>
-      <c r="F52" s="25">
+      <c r="G52" s="25">
         <f t="shared" si="5"/>
+        <v>47593</v>
+      </c>
+      <c r="H52" s="25">
+        <f>B52+30</f>
         <v>47653</v>
       </c>
-      <c r="G52" s="25">
+      <c r="I52" s="25">
         <f t="shared" si="6"/>
         <v>47653</v>
       </c>
-      <c r="H52" s="9">
+      <c r="J52" s="9">
         <f t="shared" si="17"/>
         <v>47730.299999999857</v>
       </c>
-      <c r="I52" s="9">
+      <c r="K52" s="9">
         <f t="shared" si="15"/>
         <v>47730.999999999854</v>
       </c>
-      <c r="J52" s="25">
+      <c r="L52" s="25">
         <f t="shared" si="8"/>
         <v>47745.299999999857</v>
       </c>
-      <c r="K52" s="25">
+      <c r="M52" s="25">
         <f t="shared" si="9"/>
         <v>47746.299999999857</v>
       </c>
-      <c r="L52" s="9">
+      <c r="N52" s="9">
         <f t="shared" si="18"/>
         <v>48104</v>
       </c>
-      <c r="M52" s="9">
+      <c r="O52" s="9">
         <f t="shared" si="19"/>
         <v>48108</v>
       </c>
-      <c r="N52" s="42">
+      <c r="P52" s="42">
         <f t="shared" si="12"/>
         <v>48111</v>
       </c>
-      <c r="O52" s="42">
+      <c r="Q52" s="42">
         <f t="shared" si="13"/>
         <v>48116</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>51</v>
       </c>
@@ -8820,34 +9236,36 @@
       <c r="E53" s="25"/>
       <c r="F53" s="25"/>
       <c r="G53" s="25"/>
-      <c r="H53" s="9">
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="9">
         <f t="shared" si="17"/>
         <v>47730.999999999854</v>
       </c>
-      <c r="I53" s="9">
+      <c r="K53" s="9">
         <f t="shared" si="15"/>
         <v>47731.699999999852</v>
       </c>
-      <c r="J53" s="25">
+      <c r="L53" s="25">
         <f t="shared" si="8"/>
         <v>47745.999999999854</v>
       </c>
-      <c r="K53" s="25">
+      <c r="M53" s="25">
         <f t="shared" si="9"/>
         <v>47746.999999999854</v>
       </c>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="42">
+      <c r="N53" s="23"/>
+      <c r="O53" s="23"/>
+      <c r="P53" s="42">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="O53" s="42">
+      <c r="Q53" s="42">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>52</v>
       </c>
@@ -8857,34 +9275,36 @@
       <c r="E54" s="25"/>
       <c r="F54" s="25"/>
       <c r="G54" s="25"/>
-      <c r="H54" s="9">
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="9">
         <f t="shared" si="17"/>
         <v>47731.699999999852</v>
       </c>
-      <c r="I54" s="9">
+      <c r="K54" s="9">
         <f t="shared" si="15"/>
         <v>47732.399999999849</v>
       </c>
-      <c r="J54" s="25">
+      <c r="L54" s="25">
         <f t="shared" si="8"/>
         <v>47746.699999999852</v>
       </c>
-      <c r="K54" s="25">
+      <c r="M54" s="25">
         <f t="shared" si="9"/>
         <v>47747.699999999852</v>
       </c>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="42">
+      <c r="N54" s="23"/>
+      <c r="O54" s="23"/>
+      <c r="P54" s="42">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="O54" s="42">
+      <c r="Q54" s="42">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>53</v>
       </c>
@@ -8894,34 +9314,36 @@
       <c r="E55" s="25"/>
       <c r="F55" s="25"/>
       <c r="G55" s="25"/>
-      <c r="H55" s="9">
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="9">
         <f t="shared" si="17"/>
         <v>47732.399999999849</v>
       </c>
-      <c r="I55" s="9">
+      <c r="K55" s="9">
         <f t="shared" si="15"/>
         <v>47733.099999999846</v>
       </c>
-      <c r="J55" s="25">
+      <c r="L55" s="25">
         <f t="shared" si="8"/>
         <v>47747.399999999849</v>
       </c>
-      <c r="K55" s="25">
+      <c r="M55" s="25">
         <f t="shared" si="9"/>
         <v>47748.399999999849</v>
       </c>
-      <c r="L55" s="23"/>
-      <c r="M55" s="23"/>
-      <c r="N55" s="42">
+      <c r="N55" s="23"/>
+      <c r="O55" s="23"/>
+      <c r="P55" s="42">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="O55" s="42">
+      <c r="Q55" s="42">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>54</v>
       </c>
@@ -8931,34 +9353,36 @@
       <c r="E56" s="25"/>
       <c r="F56" s="25"/>
       <c r="G56" s="25"/>
-      <c r="H56" s="9">
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="9">
         <f t="shared" si="17"/>
         <v>47733.099999999846</v>
       </c>
-      <c r="I56" s="9">
+      <c r="K56" s="9">
         <f t="shared" si="15"/>
         <v>47733.799999999843</v>
       </c>
-      <c r="J56" s="25">
+      <c r="L56" s="25">
         <f t="shared" si="8"/>
         <v>47748.099999999846</v>
       </c>
-      <c r="K56" s="25">
+      <c r="M56" s="25">
         <f t="shared" si="9"/>
         <v>47749.099999999846</v>
       </c>
-      <c r="L56" s="23"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="42">
+      <c r="N56" s="23"/>
+      <c r="O56" s="23"/>
+      <c r="P56" s="42">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="O56" s="42">
+      <c r="Q56" s="42">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>55</v>
       </c>
@@ -8968,42 +9392,45 @@
       <c r="E57" s="25"/>
       <c r="F57" s="25"/>
       <c r="G57" s="25"/>
-      <c r="H57" s="9">
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="9">
         <f t="shared" si="17"/>
         <v>47733.799999999843</v>
       </c>
-      <c r="I57" s="9">
+      <c r="K57" s="9">
         <f t="shared" si="15"/>
         <v>47734.49999999984</v>
       </c>
-      <c r="J57" s="25">
+      <c r="L57" s="25">
         <f t="shared" si="8"/>
         <v>47748.799999999843</v>
       </c>
-      <c r="K57" s="25">
+      <c r="M57" s="25">
         <f t="shared" si="9"/>
         <v>47749.799999999843</v>
       </c>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="42">
+      <c r="N57" s="23"/>
+      <c r="O57" s="23"/>
+      <c r="P57" s="42">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="O57" s="42">
+      <c r="Q57" s="42">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
